--- a/campaigns/gearbox-nigeria/Gearbox-Leads-Nigeria.xlsx
+++ b/campaigns/gearbox-nigeria/Gearbox-Leads-Nigeria.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Read me" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leads'!$A$1:$V$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leads'!$A$1:$W$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>COUNTIF(Leads!$S$2:$S$201,A16)</f>
+        <f>COUNTIF(Leads!$T$2:$T$201,A16)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B17" s="4">
-        <f>COUNTIF(Leads!$S$2:$S$201,A17)</f>
+        <f>COUNTIF(Leads!$T$2:$T$201,A17)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B18" s="4">
-        <f>COUNTIF(Leads!$S$2:$S$201,A18)</f>
+        <f>COUNTIF(Leads!$T$2:$T$201,A18)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B19" s="4">
-        <f>COUNTIF(Leads!$S$2:$S$201,A19)</f>
+        <f>COUNTIF(Leads!$T$2:$T$201,A19)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B20" s="4">
-        <f>COUNTIF(Leads!$S$2:$S$201,A20)</f>
+        <f>COUNTIF(Leads!$T$2:$T$201,A20)</f>
         <v/>
       </c>
     </row>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B21" s="4">
-        <f>COUNTIF(Leads!$S$2:$S$201,A21)</f>
+        <f>COUNTIF(Leads!$T$2:$T$201,A21)</f>
         <v/>
       </c>
     </row>
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V201"/>
+  <dimension ref="A1:W201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -816,15 +816,16 @@
     <col width="42" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="46" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -895,45 +896,50 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
+          <t>Direct/Mobile phone</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
           <t>Employees</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Suggested angle</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Salutation</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Name check</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Date sent</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Replied</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1001,31 +1007,32 @@
           <t>+234 1 448 0815</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr"/>
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>4300</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr"/>
-      <c r="S2" s="8" t="inlineStr"/>
+      <c r="S2" s="7" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="8" t="inlineStr"/>
       <c r="V2" s="8" t="inlineStr"/>
+      <c r="W2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -1091,29 +1098,34 @@
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
+          <t>+234 703 067 0238</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
           <t>4300</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P3" s="7" t="inlineStr">
+      <c r="Q3" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q3" s="7" t="inlineStr">
+      <c r="R3" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R3" s="7" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
+      <c r="S3" s="7" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="8" t="inlineStr"/>
       <c r="V3" s="8" t="inlineStr"/>
+      <c r="W3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -1179,29 +1191,34 @@
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
+          <t>+234 907 300 3046</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
           <t>4300</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr"/>
-      <c r="S4" s="8" t="inlineStr"/>
+      <c r="S4" s="7" t="inlineStr"/>
       <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="8" t="inlineStr"/>
       <c r="V4" s="8" t="inlineStr"/>
+      <c r="W4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1265,31 +1282,32 @@
           <t>+234 1 448 0815</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr"/>
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>4300</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="R5" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R5" s="7" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
+      <c r="S5" s="7" t="inlineStr"/>
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="8" t="inlineStr"/>
       <c r="V5" s="8" t="inlineStr"/>
+      <c r="W5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1357,31 +1375,32 @@
           <t>+234 1 448 0815</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P6" s="7" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q6" s="7" t="inlineStr">
+      <c r="R6" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R6" s="7" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
+      <c r="S6" s="7" t="inlineStr"/>
       <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="8" t="inlineStr"/>
       <c r="V6" s="8" t="inlineStr"/>
+      <c r="W6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1449,31 +1468,32 @@
           <t>+234 1 448 0815</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr"/>
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P7" s="7" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="R7" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R7" s="7" t="inlineStr"/>
-      <c r="S7" s="8" t="inlineStr"/>
+      <c r="S7" s="7" t="inlineStr"/>
       <c r="T7" s="8" t="inlineStr"/>
       <c r="U7" s="8" t="inlineStr"/>
       <c r="V7" s="8" t="inlineStr"/>
+      <c r="W7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1541,31 +1561,32 @@
           <t>+234 1 448 0815</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr"/>
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P8" s="7" t="inlineStr">
+      <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="R8" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R8" s="7" t="inlineStr"/>
-      <c r="S8" s="8" t="inlineStr"/>
+      <c r="S8" s="7" t="inlineStr"/>
       <c r="T8" s="8" t="inlineStr"/>
       <c r="U8" s="8" t="inlineStr"/>
       <c r="V8" s="8" t="inlineStr"/>
+      <c r="W8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1635,29 +1656,34 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
+          <t>+234 706 121 8366</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P9" s="7" t="inlineStr">
+      <c r="Q9" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q9" s="7" t="inlineStr">
+      <c r="R9" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R9" s="7" t="inlineStr"/>
-      <c r="S9" s="8" t="inlineStr"/>
+      <c r="S9" s="7" t="inlineStr"/>
       <c r="T9" s="8" t="inlineStr"/>
       <c r="U9" s="8" t="inlineStr"/>
       <c r="V9" s="8" t="inlineStr"/>
+      <c r="W9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1727,29 +1753,34 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
+          <t>+234 806 805 7486</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P10" s="7" t="inlineStr">
+      <c r="Q10" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q10" s="7" t="inlineStr">
+      <c r="R10" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R10" s="7" t="inlineStr"/>
-      <c r="S10" s="8" t="inlineStr"/>
+      <c r="S10" s="7" t="inlineStr"/>
       <c r="T10" s="8" t="inlineStr"/>
       <c r="U10" s="8" t="inlineStr"/>
       <c r="V10" s="8" t="inlineStr"/>
+      <c r="W10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1819,29 +1850,34 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
+          <t>+234 802 582 2024</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
           <t>620</t>
         </is>
       </c>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P11" s="7" t="inlineStr">
+      <c r="Q11" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q11" s="7" t="inlineStr">
+      <c r="R11" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R11" s="7" t="inlineStr"/>
-      <c r="S11" s="8" t="inlineStr"/>
+      <c r="S11" s="7" t="inlineStr"/>
       <c r="T11" s="8" t="inlineStr"/>
       <c r="U11" s="8" t="inlineStr"/>
       <c r="V11" s="8" t="inlineStr"/>
+      <c r="W11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1909,31 +1945,32 @@
           <t>+234 1 461 0669</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr">
+      <c r="N12" s="7" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>620</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="R12" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R12" s="7" t="inlineStr"/>
-      <c r="S12" s="8" t="inlineStr"/>
+      <c r="S12" s="7" t="inlineStr"/>
       <c r="T12" s="8" t="inlineStr"/>
       <c r="U12" s="8" t="inlineStr"/>
       <c r="V12" s="8" t="inlineStr"/>
+      <c r="W12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2001,31 +2038,32 @@
           <t>+234 1 461 0669</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>620</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P13" s="7" t="inlineStr">
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q13" s="7" t="inlineStr">
+      <c r="R13" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R13" s="7" t="inlineStr"/>
-      <c r="S13" s="8" t="inlineStr"/>
+      <c r="S13" s="7" t="inlineStr"/>
       <c r="T13" s="8" t="inlineStr"/>
       <c r="U13" s="8" t="inlineStr"/>
       <c r="V13" s="8" t="inlineStr"/>
+      <c r="W13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2093,31 +2131,32 @@
           <t>234-1-4610669-70</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="7" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>1300</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q14" s="7" t="inlineStr">
+      <c r="R14" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R14" s="7" t="inlineStr"/>
-      <c r="S14" s="8" t="inlineStr"/>
+      <c r="S14" s="7" t="inlineStr"/>
       <c r="T14" s="8" t="inlineStr"/>
       <c r="U14" s="8" t="inlineStr"/>
       <c r="V14" s="8" t="inlineStr"/>
+      <c r="W14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -2187,29 +2226,34 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
+          <t>+234 708 868 7481</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>building materials</t>
         </is>
       </c>
-      <c r="P15" s="7" t="inlineStr">
+      <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q15" s="7" t="inlineStr">
+      <c r="R15" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="8" t="inlineStr"/>
+      <c r="S15" s="7" t="inlineStr"/>
       <c r="T15" s="8" t="inlineStr"/>
       <c r="U15" s="8" t="inlineStr"/>
       <c r="V15" s="8" t="inlineStr"/>
+      <c r="W15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -2277,31 +2321,32 @@
           <t>+234 707 760 0080</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr">
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P16" s="7" t="inlineStr">
+      <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q16" s="7" t="inlineStr">
+      <c r="R16" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R16" s="7" t="inlineStr"/>
-      <c r="S16" s="8" t="inlineStr"/>
+      <c r="S16" s="7" t="inlineStr"/>
       <c r="T16" s="8" t="inlineStr"/>
       <c r="U16" s="8" t="inlineStr"/>
       <c r="V16" s="8" t="inlineStr"/>
+      <c r="W16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -2371,29 +2416,34 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
+          <t>+32 478 44 46 33</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
           <t>14000</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>construction</t>
         </is>
       </c>
-      <c r="P17" s="7" t="inlineStr">
+      <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q17" s="7" t="inlineStr">
+      <c r="R17" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R17" s="7" t="inlineStr"/>
-      <c r="S17" s="8" t="inlineStr"/>
+      <c r="S17" s="7" t="inlineStr"/>
       <c r="T17" s="8" t="inlineStr"/>
       <c r="U17" s="8" t="inlineStr"/>
       <c r="V17" s="8" t="inlineStr"/>
+      <c r="W17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -2463,29 +2513,34 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
+          <t>+234 818 800 0001</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
           <t>770</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>construction</t>
         </is>
       </c>
-      <c r="P18" s="7" t="inlineStr">
+      <c r="Q18" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q18" s="7" t="inlineStr">
+      <c r="R18" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R18" s="7" t="inlineStr"/>
-      <c r="S18" s="8" t="inlineStr"/>
+      <c r="S18" s="7" t="inlineStr"/>
       <c r="T18" s="8" t="inlineStr"/>
       <c r="U18" s="8" t="inlineStr"/>
       <c r="V18" s="8" t="inlineStr"/>
+      <c r="W18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -2555,29 +2610,34 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
+          <t>+234 803 929 3647</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P19" s="7" t="inlineStr">
+      <c r="Q19" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q19" s="7" t="inlineStr">
+      <c r="R19" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R19" s="7" t="inlineStr"/>
-      <c r="S19" s="8" t="inlineStr"/>
+      <c r="S19" s="7" t="inlineStr"/>
       <c r="T19" s="8" t="inlineStr"/>
       <c r="U19" s="8" t="inlineStr"/>
       <c r="V19" s="8" t="inlineStr"/>
+      <c r="W19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -2645,31 +2705,32 @@
           <t>+234 906 248 5401</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="7" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P20" s="7" t="inlineStr">
+      <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q20" s="7" t="inlineStr">
+      <c r="R20" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R20" s="7" t="inlineStr"/>
-      <c r="S20" s="8" t="inlineStr"/>
+      <c r="S20" s="7" t="inlineStr"/>
       <c r="T20" s="8" t="inlineStr"/>
       <c r="U20" s="8" t="inlineStr"/>
       <c r="V20" s="8" t="inlineStr"/>
+      <c r="W20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -2737,31 +2798,32 @@
           <t>+61 8 9232 1000</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>11000</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>mining &amp; metals</t>
         </is>
       </c>
-      <c r="P21" s="7" t="inlineStr">
+      <c r="Q21" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q21" s="7" t="inlineStr">
+      <c r="R21" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R21" s="7" t="inlineStr"/>
-      <c r="S21" s="8" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr"/>
       <c r="T21" s="8" t="inlineStr"/>
       <c r="U21" s="8" t="inlineStr"/>
       <c r="V21" s="8" t="inlineStr"/>
+      <c r="W21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -2829,31 +2891,32 @@
           <t>+234 812 515 0426</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P22" s="7" t="inlineStr">
+      <c r="Q22" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q22" s="7" t="inlineStr">
+      <c r="R22" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R22" s="7" t="inlineStr"/>
-      <c r="S22" s="8" t="inlineStr"/>
+      <c r="S22" s="7" t="inlineStr"/>
       <c r="T22" s="8" t="inlineStr"/>
       <c r="U22" s="8" t="inlineStr"/>
       <c r="V22" s="8" t="inlineStr"/>
+      <c r="W22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -2917,31 +2980,32 @@
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr">
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P23" s="7" t="inlineStr">
+      <c r="Q23" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source - mills, kilns, crushers, conveyors</t>
         </is>
       </c>
-      <c r="Q23" s="7" t="inlineStr">
+      <c r="R23" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R23" s="7" t="inlineStr"/>
-      <c r="S23" s="8" t="inlineStr"/>
+      <c r="S23" s="7" t="inlineStr"/>
       <c r="T23" s="8" t="inlineStr"/>
       <c r="U23" s="8" t="inlineStr"/>
       <c r="V23" s="8" t="inlineStr"/>
+      <c r="W23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -3009,31 +3073,32 @@
           <t>+234 705 689 1000</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr">
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>3700</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P24" s="7" t="inlineStr">
+      <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q24" s="7" t="inlineStr">
+      <c r="R24" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R24" s="7" t="inlineStr"/>
-      <c r="S24" s="8" t="inlineStr"/>
+      <c r="S24" s="7" t="inlineStr"/>
       <c r="T24" s="8" t="inlineStr"/>
       <c r="U24" s="8" t="inlineStr"/>
       <c r="V24" s="8" t="inlineStr"/>
+      <c r="W24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -3103,29 +3168,34 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
+          <t>+234 803 514 9585</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
           <t>3700</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P25" s="7" t="inlineStr">
+      <c r="Q25" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q25" s="7" t="inlineStr">
+      <c r="R25" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R25" s="7" t="inlineStr"/>
-      <c r="S25" s="8" t="inlineStr"/>
+      <c r="S25" s="7" t="inlineStr"/>
       <c r="T25" s="8" t="inlineStr"/>
       <c r="U25" s="8" t="inlineStr"/>
       <c r="V25" s="8" t="inlineStr"/>
+      <c r="W25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -3193,31 +3263,32 @@
           <t>+234 705 689 1000</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr">
+      <c r="N26" s="7" t="inlineStr"/>
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>3700</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P26" s="7" t="inlineStr">
+      <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q26" s="7" t="inlineStr">
+      <c r="R26" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R26" s="7" t="inlineStr"/>
-      <c r="S26" s="8" t="inlineStr"/>
+      <c r="S26" s="7" t="inlineStr"/>
       <c r="T26" s="8" t="inlineStr"/>
       <c r="U26" s="8" t="inlineStr"/>
       <c r="V26" s="8" t="inlineStr"/>
+      <c r="W26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -3285,31 +3356,32 @@
           <t>+234 705 689 1000</t>
         </is>
       </c>
-      <c r="N27" s="7" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr"/>
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>3700</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P27" s="7" t="inlineStr">
+      <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q27" s="7" t="inlineStr">
+      <c r="R27" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R27" s="7" t="inlineStr"/>
-      <c r="S27" s="8" t="inlineStr"/>
+      <c r="S27" s="7" t="inlineStr"/>
       <c r="T27" s="8" t="inlineStr"/>
       <c r="U27" s="8" t="inlineStr"/>
       <c r="V27" s="8" t="inlineStr"/>
+      <c r="W27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -3377,31 +3449,32 @@
           <t>+234 705 689 1000</t>
         </is>
       </c>
-      <c r="N28" s="7" t="inlineStr">
+      <c r="N28" s="7" t="inlineStr"/>
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>3700</t>
         </is>
       </c>
-      <c r="O28" s="7" t="inlineStr">
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P28" s="7" t="inlineStr">
+      <c r="Q28" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q28" s="7" t="inlineStr">
+      <c r="R28" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R28" s="7" t="inlineStr"/>
-      <c r="S28" s="8" t="inlineStr"/>
+      <c r="S28" s="7" t="inlineStr"/>
       <c r="T28" s="8" t="inlineStr"/>
       <c r="U28" s="8" t="inlineStr"/>
       <c r="V28" s="8" t="inlineStr"/>
+      <c r="W28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -3469,31 +3542,32 @@
           <t>+234 705 689 1000</t>
         </is>
       </c>
-      <c r="N29" s="7" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr"/>
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>820</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P29" s="7" t="inlineStr">
+      <c r="Q29" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q29" s="7" t="inlineStr">
+      <c r="R29" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R29" s="7" t="inlineStr"/>
-      <c r="S29" s="8" t="inlineStr"/>
+      <c r="S29" s="7" t="inlineStr"/>
       <c r="T29" s="8" t="inlineStr"/>
       <c r="U29" s="8" t="inlineStr"/>
       <c r="V29" s="8" t="inlineStr"/>
+      <c r="W29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -3561,31 +3635,32 @@
           <t>+234 705 689 1000</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr">
+      <c r="N30" s="7" t="inlineStr"/>
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>820</t>
         </is>
       </c>
-      <c r="O30" s="7" t="inlineStr">
+      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P30" s="7" t="inlineStr">
+      <c r="Q30" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q30" s="7" t="inlineStr">
+      <c r="R30" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R30" s="7" t="inlineStr"/>
-      <c r="S30" s="8" t="inlineStr"/>
+      <c r="S30" s="7" t="inlineStr"/>
       <c r="T30" s="8" t="inlineStr"/>
       <c r="U30" s="8" t="inlineStr"/>
       <c r="V30" s="8" t="inlineStr"/>
+      <c r="W30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -3655,29 +3730,34 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
+          <t>+1 804-779-5289</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
           <t>820</t>
         </is>
       </c>
-      <c r="O31" s="7" t="inlineStr">
+      <c r="P31" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P31" s="7" t="inlineStr">
+      <c r="Q31" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q31" s="7" t="inlineStr">
+      <c r="R31" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R31" s="7" t="inlineStr"/>
-      <c r="S31" s="8" t="inlineStr"/>
+      <c r="S31" s="7" t="inlineStr"/>
       <c r="T31" s="8" t="inlineStr"/>
       <c r="U31" s="8" t="inlineStr"/>
       <c r="V31" s="8" t="inlineStr"/>
+      <c r="W31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -3745,31 +3825,32 @@
           <t>+234 1 461 0669</t>
         </is>
       </c>
-      <c r="N32" s="7" t="inlineStr">
+      <c r="N32" s="7" t="inlineStr"/>
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>560</t>
         </is>
       </c>
-      <c r="O32" s="7" t="inlineStr">
+      <c r="P32" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P32" s="7" t="inlineStr">
+      <c r="Q32" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q32" s="7" t="inlineStr">
+      <c r="R32" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R32" s="7" t="inlineStr"/>
-      <c r="S32" s="8" t="inlineStr"/>
+      <c r="S32" s="7" t="inlineStr"/>
       <c r="T32" s="8" t="inlineStr"/>
       <c r="U32" s="8" t="inlineStr"/>
       <c r="V32" s="8" t="inlineStr"/>
+      <c r="W32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -3839,29 +3920,34 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
+          <t>+234 902 410 0902</t>
+        </is>
+      </c>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
           <t>560</t>
         </is>
       </c>
-      <c r="O33" s="7" t="inlineStr">
+      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P33" s="7" t="inlineStr">
+      <c r="Q33" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q33" s="7" t="inlineStr">
+      <c r="R33" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R33" s="7" t="inlineStr"/>
-      <c r="S33" s="8" t="inlineStr"/>
+      <c r="S33" s="7" t="inlineStr"/>
       <c r="T33" s="8" t="inlineStr"/>
       <c r="U33" s="8" t="inlineStr"/>
       <c r="V33" s="8" t="inlineStr"/>
+      <c r="W33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -3925,35 +4011,36 @@
           <t>234-1- 4610669-70</t>
         </is>
       </c>
-      <c r="N34" s="7" t="inlineStr">
+      <c r="N34" s="7" t="inlineStr"/>
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="O34" s="7" t="inlineStr">
+      <c r="P34" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P34" s="7" t="inlineStr">
+      <c r="Q34" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q34" s="7" t="inlineStr">
+      <c r="R34" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R34" s="9" t="inlineStr">
+      <c r="S34" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S34" s="8" t="inlineStr"/>
       <c r="T34" s="8" t="inlineStr"/>
       <c r="U34" s="8" t="inlineStr"/>
       <c r="V34" s="8" t="inlineStr"/>
+      <c r="W34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -4023,29 +4110,34 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
+          <t>+234 805 279 7438</t>
+        </is>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
           <t>271000</t>
         </is>
       </c>
-      <c r="O35" s="7" t="inlineStr">
+      <c r="P35" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P35" s="7" t="inlineStr">
+      <c r="Q35" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q35" s="7" t="inlineStr">
+      <c r="R35" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R35" s="7" t="inlineStr"/>
-      <c r="S35" s="8" t="inlineStr"/>
+      <c r="S35" s="7" t="inlineStr"/>
       <c r="T35" s="8" t="inlineStr"/>
       <c r="U35" s="8" t="inlineStr"/>
       <c r="V35" s="8" t="inlineStr"/>
+      <c r="W35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -4115,33 +4207,38 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
+          <t>+234 805 279 7380</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
           <t>271000</t>
         </is>
       </c>
-      <c r="O36" s="7" t="inlineStr">
+      <c r="P36" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P36" s="7" t="inlineStr">
+      <c r="Q36" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q36" s="7" t="inlineStr">
+      <c r="R36" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R36" s="9" t="inlineStr">
+      <c r="S36" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S36" s="8" t="inlineStr"/>
       <c r="T36" s="8" t="inlineStr"/>
       <c r="U36" s="8" t="inlineStr"/>
       <c r="V36" s="8" t="inlineStr"/>
+      <c r="W36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -4209,31 +4306,32 @@
           <t>+31 33 713 3333</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr">
+      <c r="N37" s="7" t="inlineStr"/>
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="O37" s="7" t="inlineStr">
+      <c r="P37" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P37" s="7" t="inlineStr">
+      <c r="Q37" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q37" s="7" t="inlineStr">
+      <c r="R37" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R37" s="7" t="inlineStr"/>
-      <c r="S37" s="8" t="inlineStr"/>
+      <c r="S37" s="7" t="inlineStr"/>
       <c r="T37" s="8" t="inlineStr"/>
       <c r="U37" s="8" t="inlineStr"/>
       <c r="V37" s="8" t="inlineStr"/>
+      <c r="W37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -4303,33 +4401,38 @@
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
+          <t>+234 802 681 1608</t>
+        </is>
+      </c>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="O38" s="7" t="inlineStr">
+      <c r="P38" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P38" s="7" t="inlineStr">
+      <c r="Q38" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q38" s="7" t="inlineStr">
+      <c r="R38" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R38" s="9" t="inlineStr">
+      <c r="S38" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S38" s="8" t="inlineStr"/>
       <c r="T38" s="8" t="inlineStr"/>
       <c r="U38" s="8" t="inlineStr"/>
       <c r="V38" s="8" t="inlineStr"/>
+      <c r="W38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -4397,31 +4500,32 @@
           <t>+31 33 713 3333</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="N39" s="7" t="inlineStr"/>
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="O39" s="7" t="inlineStr">
+      <c r="P39" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P39" s="7" t="inlineStr">
+      <c r="Q39" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q39" s="7" t="inlineStr">
+      <c r="R39" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R39" s="7" t="inlineStr"/>
-      <c r="S39" s="8" t="inlineStr"/>
+      <c r="S39" s="7" t="inlineStr"/>
       <c r="T39" s="8" t="inlineStr"/>
       <c r="U39" s="8" t="inlineStr"/>
       <c r="V39" s="8" t="inlineStr"/>
+      <c r="W39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -4489,31 +4593,32 @@
           <t>+31 33 713 3333</t>
         </is>
       </c>
-      <c r="N40" s="7" t="inlineStr">
+      <c r="N40" s="7" t="inlineStr"/>
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="O40" s="7" t="inlineStr">
+      <c r="P40" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P40" s="7" t="inlineStr">
+      <c r="Q40" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q40" s="7" t="inlineStr">
+      <c r="R40" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R40" s="7" t="inlineStr"/>
-      <c r="S40" s="8" t="inlineStr"/>
+      <c r="S40" s="7" t="inlineStr"/>
       <c r="T40" s="8" t="inlineStr"/>
       <c r="U40" s="8" t="inlineStr"/>
       <c r="V40" s="8" t="inlineStr"/>
+      <c r="W40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -4583,29 +4688,34 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
+          <t>+234 806 745 6126</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="O41" s="7" t="inlineStr">
+      <c r="P41" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P41" s="7" t="inlineStr">
+      <c r="Q41" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q41" s="7" t="inlineStr">
+      <c r="R41" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R41" s="7" t="inlineStr"/>
-      <c r="S41" s="8" t="inlineStr"/>
+      <c r="S41" s="7" t="inlineStr"/>
       <c r="T41" s="8" t="inlineStr"/>
       <c r="U41" s="8" t="inlineStr"/>
       <c r="V41" s="8" t="inlineStr"/>
+      <c r="W41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -4673,31 +4783,32 @@
           <t>+41 41 726 01 10</t>
         </is>
       </c>
-      <c r="N42" s="7" t="inlineStr">
+      <c r="N42" s="7" t="inlineStr"/>
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>33000</t>
         </is>
       </c>
-      <c r="O42" s="7" t="inlineStr">
+      <c r="P42" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P42" s="7" t="inlineStr">
+      <c r="Q42" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q42" s="7" t="inlineStr">
+      <c r="R42" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R42" s="7" t="inlineStr"/>
-      <c r="S42" s="8" t="inlineStr"/>
+      <c r="S42" s="7" t="inlineStr"/>
       <c r="T42" s="8" t="inlineStr"/>
       <c r="U42" s="8" t="inlineStr"/>
       <c r="V42" s="8" t="inlineStr"/>
+      <c r="W42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -4765,31 +4876,32 @@
           <t>+41 41 726 01 10</t>
         </is>
       </c>
-      <c r="N43" s="7" t="inlineStr">
+      <c r="N43" s="7" t="inlineStr"/>
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>33000</t>
         </is>
       </c>
-      <c r="O43" s="7" t="inlineStr">
+      <c r="P43" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P43" s="7" t="inlineStr">
+      <c r="Q43" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q43" s="7" t="inlineStr">
+      <c r="R43" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R43" s="7" t="inlineStr"/>
-      <c r="S43" s="8" t="inlineStr"/>
+      <c r="S43" s="7" t="inlineStr"/>
       <c r="T43" s="8" t="inlineStr"/>
       <c r="U43" s="8" t="inlineStr"/>
       <c r="V43" s="8" t="inlineStr"/>
+      <c r="W43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -4857,31 +4969,32 @@
           <t>+41 41 726 01 10</t>
         </is>
       </c>
-      <c r="N44" s="7" t="inlineStr">
+      <c r="N44" s="7" t="inlineStr"/>
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>33000</t>
         </is>
       </c>
-      <c r="O44" s="7" t="inlineStr">
+      <c r="P44" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P44" s="7" t="inlineStr">
+      <c r="Q44" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q44" s="7" t="inlineStr">
+      <c r="R44" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R44" s="7" t="inlineStr"/>
-      <c r="S44" s="8" t="inlineStr"/>
+      <c r="S44" s="7" t="inlineStr"/>
       <c r="T44" s="8" t="inlineStr"/>
       <c r="U44" s="8" t="inlineStr"/>
       <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -4949,31 +5062,32 @@
           <t>+41 41 726 01 10</t>
         </is>
       </c>
-      <c r="N45" s="7" t="inlineStr">
+      <c r="N45" s="7" t="inlineStr"/>
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>33000</t>
         </is>
       </c>
-      <c r="O45" s="7" t="inlineStr">
+      <c r="P45" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P45" s="7" t="inlineStr">
+      <c r="Q45" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q45" s="7" t="inlineStr">
+      <c r="R45" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R45" s="7" t="inlineStr"/>
-      <c r="S45" s="8" t="inlineStr"/>
+      <c r="S45" s="7" t="inlineStr"/>
       <c r="T45" s="8" t="inlineStr"/>
       <c r="U45" s="8" t="inlineStr"/>
       <c r="V45" s="8" t="inlineStr"/>
+      <c r="W45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -5041,31 +5155,32 @@
           <t>+41 41 726 01 10</t>
         </is>
       </c>
-      <c r="N46" s="7" t="inlineStr">
+      <c r="N46" s="7" t="inlineStr"/>
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>33000</t>
         </is>
       </c>
-      <c r="O46" s="7" t="inlineStr">
+      <c r="P46" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P46" s="7" t="inlineStr">
+      <c r="Q46" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q46" s="7" t="inlineStr">
+      <c r="R46" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R46" s="7" t="inlineStr"/>
-      <c r="S46" s="8" t="inlineStr"/>
+      <c r="S46" s="7" t="inlineStr"/>
       <c r="T46" s="8" t="inlineStr"/>
       <c r="U46" s="8" t="inlineStr"/>
       <c r="V46" s="8" t="inlineStr"/>
+      <c r="W46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -5133,31 +5248,32 @@
           <t>+234 805 690 0900</t>
         </is>
       </c>
-      <c r="N47" s="7" t="inlineStr">
+      <c r="N47" s="7" t="inlineStr"/>
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="O47" s="7" t="inlineStr">
+      <c r="P47" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P47" s="7" t="inlineStr">
+      <c r="Q47" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q47" s="7" t="inlineStr">
+      <c r="R47" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R47" s="7" t="inlineStr"/>
-      <c r="S47" s="8" t="inlineStr"/>
+      <c r="S47" s="7" t="inlineStr"/>
       <c r="T47" s="8" t="inlineStr"/>
       <c r="U47" s="8" t="inlineStr"/>
       <c r="V47" s="8" t="inlineStr"/>
+      <c r="W47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -5227,29 +5343,34 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
+          <t>+234 803 452 5035</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="O48" s="7" t="inlineStr">
+      <c r="P48" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P48" s="7" t="inlineStr">
+      <c r="Q48" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q48" s="7" t="inlineStr">
+      <c r="R48" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R48" s="7" t="inlineStr"/>
-      <c r="S48" s="8" t="inlineStr"/>
+      <c r="S48" s="7" t="inlineStr"/>
       <c r="T48" s="8" t="inlineStr"/>
       <c r="U48" s="8" t="inlineStr"/>
       <c r="V48" s="8" t="inlineStr"/>
+      <c r="W48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -5315,29 +5436,34 @@
       <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="7" t="inlineStr">
         <is>
+          <t>+91 90490 08586</t>
+        </is>
+      </c>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="O49" s="7" t="inlineStr">
+      <c r="P49" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P49" s="7" t="inlineStr">
+      <c r="Q49" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q49" s="7" t="inlineStr">
+      <c r="R49" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R49" s="7" t="inlineStr"/>
-      <c r="S49" s="8" t="inlineStr"/>
+      <c r="S49" s="7" t="inlineStr"/>
       <c r="T49" s="8" t="inlineStr"/>
       <c r="U49" s="8" t="inlineStr"/>
       <c r="V49" s="8" t="inlineStr"/>
+      <c r="W49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -5401,31 +5527,32 @@
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr">
+      <c r="N50" s="7" t="inlineStr"/>
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="O50" s="7" t="inlineStr">
+      <c r="P50" s="7" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="P50" s="7" t="inlineStr">
+      <c r="Q50" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q50" s="7" t="inlineStr">
+      <c r="R50" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R50" s="7" t="inlineStr"/>
-      <c r="S50" s="8" t="inlineStr"/>
+      <c r="S50" s="7" t="inlineStr"/>
       <c r="T50" s="8" t="inlineStr"/>
       <c r="U50" s="8" t="inlineStr"/>
       <c r="V50" s="8" t="inlineStr"/>
+      <c r="W50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -5489,31 +5616,32 @@
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr">
+      <c r="N51" s="7" t="inlineStr"/>
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="O51" s="7" t="inlineStr">
+      <c r="P51" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P51" s="7" t="inlineStr">
+      <c r="Q51" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q51" s="7" t="inlineStr">
+      <c r="R51" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R51" s="7" t="inlineStr"/>
-      <c r="S51" s="8" t="inlineStr"/>
+      <c r="S51" s="7" t="inlineStr"/>
       <c r="T51" s="8" t="inlineStr"/>
       <c r="U51" s="8" t="inlineStr"/>
       <c r="V51" s="8" t="inlineStr"/>
+      <c r="W51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -5581,31 +5709,32 @@
           <t>+234 1 270 9100</t>
         </is>
       </c>
-      <c r="N52" s="7" t="inlineStr">
+      <c r="N52" s="7" t="inlineStr"/>
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="O52" s="7" t="inlineStr">
+      <c r="P52" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P52" s="7" t="inlineStr">
+      <c r="Q52" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q52" s="7" t="inlineStr">
+      <c r="R52" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R52" s="7" t="inlineStr"/>
-      <c r="S52" s="8" t="inlineStr"/>
+      <c r="S52" s="7" t="inlineStr"/>
       <c r="T52" s="8" t="inlineStr"/>
       <c r="U52" s="8" t="inlineStr"/>
       <c r="V52" s="8" t="inlineStr"/>
+      <c r="W52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -5673,31 +5802,32 @@
           <t>+234 905 380 4042</t>
         </is>
       </c>
-      <c r="N53" s="7" t="inlineStr">
+      <c r="N53" s="7" t="inlineStr"/>
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="O53" s="7" t="inlineStr">
+      <c r="P53" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P53" s="7" t="inlineStr">
+      <c r="Q53" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q53" s="7" t="inlineStr">
+      <c r="R53" s="7" t="inlineStr">
         <is>
           <t>Ms.</t>
         </is>
       </c>
-      <c r="R53" s="7" t="inlineStr"/>
-      <c r="S53" s="8" t="inlineStr"/>
+      <c r="S53" s="7" t="inlineStr"/>
       <c r="T53" s="8" t="inlineStr"/>
       <c r="U53" s="8" t="inlineStr"/>
-      <c r="V53" s="8" t="inlineStr">
+      <c r="V53" s="8" t="inlineStr"/>
+      <c r="W53" s="8" t="inlineStr">
         <is>
           <t>email is extrapolated, not verified - use with care</t>
         </is>
@@ -5771,29 +5901,34 @@
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
+          <t>+216 54 211 198</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="O54" s="7" t="inlineStr">
+      <c r="P54" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P54" s="7" t="inlineStr">
+      <c r="Q54" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q54" s="7" t="inlineStr">
+      <c r="R54" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R54" s="7" t="inlineStr"/>
-      <c r="S54" s="8" t="inlineStr"/>
+      <c r="S54" s="7" t="inlineStr"/>
       <c r="T54" s="8" t="inlineStr"/>
       <c r="U54" s="8" t="inlineStr"/>
       <c r="V54" s="8" t="inlineStr"/>
+      <c r="W54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -5861,31 +5996,32 @@
           <t>+234 1 454 5278</t>
         </is>
       </c>
-      <c r="N55" s="7" t="inlineStr">
+      <c r="N55" s="7" t="inlineStr"/>
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="O55" s="7" t="inlineStr">
+      <c r="P55" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P55" s="7" t="inlineStr">
+      <c r="Q55" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q55" s="7" t="inlineStr">
+      <c r="R55" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R55" s="7" t="inlineStr"/>
-      <c r="S55" s="8" t="inlineStr"/>
+      <c r="S55" s="7" t="inlineStr"/>
       <c r="T55" s="8" t="inlineStr"/>
       <c r="U55" s="8" t="inlineStr"/>
       <c r="V55" s="8" t="inlineStr"/>
+      <c r="W55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -5953,31 +6089,32 @@
           <t>+234 1 454 5278</t>
         </is>
       </c>
-      <c r="N56" s="7" t="inlineStr">
+      <c r="N56" s="7" t="inlineStr"/>
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="O56" s="7" t="inlineStr">
+      <c r="P56" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P56" s="7" t="inlineStr">
+      <c r="Q56" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q56" s="7" t="inlineStr">
+      <c r="R56" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R56" s="7" t="inlineStr"/>
-      <c r="S56" s="8" t="inlineStr"/>
+      <c r="S56" s="7" t="inlineStr"/>
       <c r="T56" s="8" t="inlineStr"/>
       <c r="U56" s="8" t="inlineStr"/>
       <c r="V56" s="8" t="inlineStr"/>
+      <c r="W56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -6045,31 +6182,32 @@
           <t>+234 809 393 1020</t>
         </is>
       </c>
-      <c r="N57" s="7" t="inlineStr">
+      <c r="N57" s="7" t="inlineStr"/>
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O57" s="7" t="inlineStr">
+      <c r="P57" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P57" s="7" t="inlineStr">
+      <c r="Q57" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q57" s="7" t="inlineStr">
+      <c r="R57" s="7" t="inlineStr">
         <is>
           <t>Ms.</t>
         </is>
       </c>
-      <c r="R57" s="7" t="inlineStr"/>
-      <c r="S57" s="8" t="inlineStr"/>
+      <c r="S57" s="7" t="inlineStr"/>
       <c r="T57" s="8" t="inlineStr"/>
       <c r="U57" s="8" t="inlineStr"/>
       <c r="V57" s="8" t="inlineStr"/>
+      <c r="W57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -6133,31 +6271,32 @@
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr">
+      <c r="N58" s="7" t="inlineStr"/>
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="O58" s="7" t="inlineStr">
+      <c r="P58" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P58" s="7" t="inlineStr">
+      <c r="Q58" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q58" s="7" t="inlineStr">
+      <c r="R58" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R58" s="7" t="inlineStr"/>
-      <c r="S58" s="8" t="inlineStr"/>
+      <c r="S58" s="7" t="inlineStr"/>
       <c r="T58" s="8" t="inlineStr"/>
       <c r="U58" s="8" t="inlineStr"/>
       <c r="V58" s="8" t="inlineStr"/>
+      <c r="W58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -6221,35 +6360,36 @@
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr"/>
-      <c r="N59" s="7" t="inlineStr">
+      <c r="N59" s="7" t="inlineStr"/>
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O59" s="7" t="inlineStr">
+      <c r="P59" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P59" s="7" t="inlineStr">
+      <c r="Q59" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q59" s="7" t="inlineStr">
+      <c r="R59" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R59" s="9" t="inlineStr">
+      <c r="S59" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S59" s="8" t="inlineStr"/>
       <c r="T59" s="8" t="inlineStr"/>
       <c r="U59" s="8" t="inlineStr"/>
       <c r="V59" s="8" t="inlineStr"/>
+      <c r="W59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -6319,29 +6459,34 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
+          <t>+234 907 006 7582</t>
+        </is>
+      </c>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
           <t>16000</t>
         </is>
       </c>
-      <c r="O60" s="7" t="inlineStr">
+      <c r="P60" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P60" s="7" t="inlineStr">
+      <c r="Q60" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q60" s="7" t="inlineStr">
+      <c r="R60" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R60" s="7" t="inlineStr"/>
-      <c r="S60" s="8" t="inlineStr"/>
+      <c r="S60" s="7" t="inlineStr"/>
       <c r="T60" s="8" t="inlineStr"/>
       <c r="U60" s="8" t="inlineStr"/>
       <c r="V60" s="8" t="inlineStr"/>
+      <c r="W60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -6409,31 +6554,32 @@
           <t>+65 6387 7777</t>
         </is>
       </c>
-      <c r="N61" s="7" t="inlineStr">
+      <c r="N61" s="7" t="inlineStr"/>
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>16000</t>
         </is>
       </c>
-      <c r="O61" s="7" t="inlineStr">
+      <c r="P61" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P61" s="7" t="inlineStr">
+      <c r="Q61" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q61" s="7" t="inlineStr">
+      <c r="R61" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R61" s="7" t="inlineStr"/>
-      <c r="S61" s="8" t="inlineStr"/>
+      <c r="S61" s="7" t="inlineStr"/>
       <c r="T61" s="8" t="inlineStr"/>
       <c r="U61" s="8" t="inlineStr"/>
       <c r="V61" s="8" t="inlineStr"/>
+      <c r="W61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -6499,29 +6645,34 @@
       <c r="M62" s="7" t="inlineStr"/>
       <c r="N62" s="7" t="inlineStr">
         <is>
+          <t>+234 805 553 9133</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="O62" s="7" t="inlineStr">
+      <c r="P62" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P62" s="7" t="inlineStr">
+      <c r="Q62" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q62" s="7" t="inlineStr">
+      <c r="R62" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R62" s="7" t="inlineStr"/>
-      <c r="S62" s="8" t="inlineStr"/>
+      <c r="S62" s="7" t="inlineStr"/>
       <c r="T62" s="8" t="inlineStr"/>
       <c r="U62" s="8" t="inlineStr"/>
       <c r="V62" s="8" t="inlineStr"/>
+      <c r="W62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -6589,31 +6740,32 @@
           <t>+234 803 324 9025</t>
         </is>
       </c>
-      <c r="N63" s="7" t="inlineStr">
+      <c r="N63" s="7" t="inlineStr"/>
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="O63" s="7" t="inlineStr">
+      <c r="P63" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P63" s="7" t="inlineStr">
+      <c r="Q63" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q63" s="7" t="inlineStr">
+      <c r="R63" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R63" s="7" t="inlineStr"/>
-      <c r="S63" s="8" t="inlineStr"/>
+      <c r="S63" s="7" t="inlineStr"/>
       <c r="T63" s="8" t="inlineStr"/>
       <c r="U63" s="8" t="inlineStr"/>
       <c r="V63" s="8" t="inlineStr"/>
+      <c r="W63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -6675,29 +6827,34 @@
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="7" t="inlineStr">
         <is>
+          <t>+1 262-260-2154</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
           <t>7600</t>
         </is>
       </c>
-      <c r="O64" s="7" t="inlineStr">
+      <c r="P64" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P64" s="7" t="inlineStr">
+      <c r="Q64" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q64" s="7" t="inlineStr">
+      <c r="R64" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R64" s="7" t="inlineStr"/>
-      <c r="S64" s="8" t="inlineStr"/>
+      <c r="S64" s="7" t="inlineStr"/>
       <c r="T64" s="8" t="inlineStr"/>
       <c r="U64" s="8" t="inlineStr"/>
       <c r="V64" s="8" t="inlineStr"/>
+      <c r="W64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -6761,31 +6918,32 @@
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr"/>
-      <c r="N65" s="7" t="inlineStr">
+      <c r="N65" s="7" t="inlineStr"/>
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O65" s="7" t="inlineStr">
+      <c r="P65" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P65" s="7" t="inlineStr">
+      <c r="Q65" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q65" s="7" t="inlineStr">
+      <c r="R65" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R65" s="7" t="inlineStr"/>
-      <c r="S65" s="8" t="inlineStr"/>
+      <c r="S65" s="7" t="inlineStr"/>
       <c r="T65" s="8" t="inlineStr"/>
       <c r="U65" s="8" t="inlineStr"/>
       <c r="V65" s="8" t="inlineStr"/>
+      <c r="W65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -6855,29 +7013,34 @@
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
+          <t>+234 705 217 0850</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="O66" s="7" t="inlineStr">
+      <c r="P66" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P66" s="7" t="inlineStr">
+      <c r="Q66" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q66" s="7" t="inlineStr">
+      <c r="R66" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R66" s="7" t="inlineStr"/>
-      <c r="S66" s="8" t="inlineStr"/>
+      <c r="S66" s="7" t="inlineStr"/>
       <c r="T66" s="8" t="inlineStr"/>
       <c r="U66" s="8" t="inlineStr"/>
       <c r="V66" s="8" t="inlineStr"/>
+      <c r="W66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -6947,29 +7110,34 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
+          <t>+234 803 351 4546</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="O67" s="7" t="inlineStr">
+      <c r="P67" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P67" s="7" t="inlineStr">
+      <c r="Q67" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q67" s="7" t="inlineStr">
+      <c r="R67" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R67" s="7" t="inlineStr"/>
-      <c r="S67" s="8" t="inlineStr"/>
+      <c r="S67" s="7" t="inlineStr"/>
       <c r="T67" s="8" t="inlineStr"/>
       <c r="U67" s="8" t="inlineStr"/>
       <c r="V67" s="8" t="inlineStr"/>
+      <c r="W67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -7039,29 +7207,34 @@
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
+          <t>+234 803 877 6339</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="O68" s="7" t="inlineStr">
+      <c r="P68" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P68" s="7" t="inlineStr">
+      <c r="Q68" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q68" s="7" t="inlineStr">
+      <c r="R68" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R68" s="7" t="inlineStr"/>
-      <c r="S68" s="8" t="inlineStr"/>
+      <c r="S68" s="7" t="inlineStr"/>
       <c r="T68" s="8" t="inlineStr"/>
       <c r="U68" s="8" t="inlineStr"/>
       <c r="V68" s="8" t="inlineStr"/>
+      <c r="W68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -7131,29 +7304,34 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
+          <t>+234 803 457 8885</t>
+        </is>
+      </c>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="O69" s="7" t="inlineStr">
+      <c r="P69" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P69" s="7" t="inlineStr">
+      <c r="Q69" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q69" s="7" t="inlineStr">
+      <c r="R69" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R69" s="7" t="inlineStr"/>
-      <c r="S69" s="8" t="inlineStr"/>
+      <c r="S69" s="7" t="inlineStr"/>
       <c r="T69" s="8" t="inlineStr"/>
       <c r="U69" s="8" t="inlineStr"/>
       <c r="V69" s="8" t="inlineStr"/>
+      <c r="W69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -7221,31 +7399,32 @@
           <t>+65 6339 4100</t>
         </is>
       </c>
-      <c r="N70" s="7" t="inlineStr">
+      <c r="N70" s="7" t="inlineStr"/>
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="O70" s="7" t="inlineStr">
+      <c r="P70" s="7" t="inlineStr">
         <is>
           <t>food &amp; beverages</t>
         </is>
       </c>
-      <c r="P70" s="7" t="inlineStr">
+      <c r="Q70" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q70" s="7" t="inlineStr">
+      <c r="R70" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R70" s="7" t="inlineStr"/>
-      <c r="S70" s="8" t="inlineStr"/>
+      <c r="S70" s="7" t="inlineStr"/>
       <c r="T70" s="8" t="inlineStr"/>
       <c r="U70" s="8" t="inlineStr"/>
       <c r="V70" s="8" t="inlineStr"/>
+      <c r="W70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -7309,31 +7488,32 @@
           <t>+234 806 036 1068</t>
         </is>
       </c>
-      <c r="N71" s="7" t="inlineStr">
+      <c r="N71" s="7" t="inlineStr"/>
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="O71" s="7" t="inlineStr">
+      <c r="P71" s="7" t="inlineStr">
         <is>
           <t>farming</t>
         </is>
       </c>
-      <c r="P71" s="7" t="inlineStr">
+      <c r="Q71" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q71" s="7" t="inlineStr">
+      <c r="R71" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R71" s="7" t="inlineStr"/>
-      <c r="S71" s="8" t="inlineStr"/>
+      <c r="S71" s="7" t="inlineStr"/>
       <c r="T71" s="8" t="inlineStr"/>
       <c r="U71" s="8" t="inlineStr"/>
       <c r="V71" s="8" t="inlineStr"/>
+      <c r="W71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -7401,31 +7581,32 @@
           <t>+1 800-527-3295</t>
         </is>
       </c>
-      <c r="N72" s="7" t="inlineStr">
+      <c r="N72" s="7" t="inlineStr"/>
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="O72" s="7" t="inlineStr">
+      <c r="P72" s="7" t="inlineStr">
         <is>
           <t>plastics</t>
         </is>
       </c>
-      <c r="P72" s="7" t="inlineStr">
+      <c r="Q72" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q72" s="7" t="inlineStr">
+      <c r="R72" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R72" s="7" t="inlineStr"/>
-      <c r="S72" s="8" t="inlineStr"/>
+      <c r="S72" s="7" t="inlineStr"/>
       <c r="T72" s="8" t="inlineStr"/>
       <c r="U72" s="8" t="inlineStr"/>
       <c r="V72" s="8" t="inlineStr"/>
+      <c r="W72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -7493,31 +7674,32 @@
           <t>+234 903 902 2200</t>
         </is>
       </c>
-      <c r="N73" s="7" t="inlineStr">
+      <c r="N73" s="7" t="inlineStr"/>
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O73" s="7" t="inlineStr">
+      <c r="P73" s="7" t="inlineStr">
         <is>
           <t>food production</t>
         </is>
       </c>
-      <c r="P73" s="7" t="inlineStr">
+      <c r="Q73" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q73" s="7" t="inlineStr">
+      <c r="R73" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R73" s="7" t="inlineStr"/>
-      <c r="S73" s="8" t="inlineStr"/>
+      <c r="S73" s="7" t="inlineStr"/>
       <c r="T73" s="8" t="inlineStr"/>
       <c r="U73" s="8" t="inlineStr"/>
       <c r="V73" s="8" t="inlineStr"/>
+      <c r="W73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -7585,31 +7767,32 @@
           <t>+65 6292 7316</t>
         </is>
       </c>
-      <c r="N74" s="7" t="inlineStr">
+      <c r="N74" s="7" t="inlineStr"/>
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="O74" s="7" t="inlineStr">
+      <c r="P74" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P74" s="7" t="inlineStr">
+      <c r="Q74" s="7" t="inlineStr">
         <is>
           <t>Mills and lines run nonstop - stock drive spares</t>
         </is>
       </c>
-      <c r="Q74" s="7" t="inlineStr">
+      <c r="R74" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R74" s="7" t="inlineStr"/>
-      <c r="S74" s="8" t="inlineStr"/>
+      <c r="S74" s="7" t="inlineStr"/>
       <c r="T74" s="8" t="inlineStr"/>
       <c r="U74" s="8" t="inlineStr"/>
       <c r="V74" s="8" t="inlineStr"/>
+      <c r="W74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
@@ -7675,29 +7858,34 @@
       <c r="M75" s="7" t="inlineStr"/>
       <c r="N75" s="7" t="inlineStr">
         <is>
+          <t>+234 815 085 4347</t>
+        </is>
+      </c>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
           <t>970</t>
         </is>
       </c>
-      <c r="O75" s="7" t="inlineStr">
+      <c r="P75" s="7" t="inlineStr">
         <is>
           <t>packaging &amp; containers</t>
         </is>
       </c>
-      <c r="P75" s="7" t="inlineStr">
+      <c r="Q75" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q75" s="7" t="inlineStr">
+      <c r="R75" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R75" s="7" t="inlineStr"/>
-      <c r="S75" s="8" t="inlineStr"/>
+      <c r="S75" s="7" t="inlineStr"/>
       <c r="T75" s="8" t="inlineStr"/>
       <c r="U75" s="8" t="inlineStr"/>
       <c r="V75" s="8" t="inlineStr"/>
+      <c r="W75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -7763,29 +7951,34 @@
       <c r="M76" s="7" t="inlineStr"/>
       <c r="N76" s="7" t="inlineStr">
         <is>
+          <t>+234 705 222 2235</t>
+        </is>
+      </c>
+      <c r="O76" s="7" t="inlineStr">
+        <is>
           <t>970</t>
         </is>
       </c>
-      <c r="O76" s="7" t="inlineStr">
+      <c r="P76" s="7" t="inlineStr">
         <is>
           <t>packaging &amp; containers</t>
         </is>
       </c>
-      <c r="P76" s="7" t="inlineStr">
+      <c r="Q76" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q76" s="7" t="inlineStr">
+      <c r="R76" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R76" s="7" t="inlineStr"/>
-      <c r="S76" s="8" t="inlineStr"/>
+      <c r="S76" s="7" t="inlineStr"/>
       <c r="T76" s="8" t="inlineStr"/>
       <c r="U76" s="8" t="inlineStr"/>
       <c r="V76" s="8" t="inlineStr"/>
+      <c r="W76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -7849,31 +8042,32 @@
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr"/>
-      <c r="N77" s="7" t="inlineStr">
+      <c r="N77" s="7" t="inlineStr"/>
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>970</t>
         </is>
       </c>
-      <c r="O77" s="7" t="inlineStr">
+      <c r="P77" s="7" t="inlineStr">
         <is>
           <t>packaging &amp; containers</t>
         </is>
       </c>
-      <c r="P77" s="7" t="inlineStr">
+      <c r="Q77" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q77" s="7" t="inlineStr">
+      <c r="R77" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R77" s="7" t="inlineStr"/>
-      <c r="S77" s="8" t="inlineStr"/>
+      <c r="S77" s="7" t="inlineStr"/>
       <c r="T77" s="8" t="inlineStr"/>
       <c r="U77" s="8" t="inlineStr"/>
       <c r="V77" s="8" t="inlineStr"/>
+      <c r="W77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -7941,31 +8135,32 @@
           <t>+234 201 906 3200</t>
         </is>
       </c>
-      <c r="N78" s="7" t="inlineStr">
+      <c r="N78" s="7" t="inlineStr"/>
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="O78" s="7" t="inlineStr">
+      <c r="P78" s="7" t="inlineStr">
         <is>
           <t>glass, ceramics &amp; concrete</t>
         </is>
       </c>
-      <c r="P78" s="7" t="inlineStr">
+      <c r="Q78" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q78" s="7" t="inlineStr">
+      <c r="R78" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R78" s="7" t="inlineStr"/>
-      <c r="S78" s="8" t="inlineStr"/>
+      <c r="S78" s="7" t="inlineStr"/>
       <c r="T78" s="8" t="inlineStr"/>
       <c r="U78" s="8" t="inlineStr"/>
       <c r="V78" s="8" t="inlineStr"/>
+      <c r="W78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -8035,29 +8230,34 @@
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
+          <t>+234 806 960 7287</t>
+        </is>
+      </c>
+      <c r="O79" s="7" t="inlineStr">
+        <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="O79" s="7" t="inlineStr">
+      <c r="P79" s="7" t="inlineStr">
         <is>
           <t>packaging &amp; containers</t>
         </is>
       </c>
-      <c r="P79" s="7" t="inlineStr">
+      <c r="Q79" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q79" s="7" t="inlineStr">
+      <c r="R79" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R79" s="7" t="inlineStr"/>
-      <c r="S79" s="8" t="inlineStr"/>
+      <c r="S79" s="7" t="inlineStr"/>
       <c r="T79" s="8" t="inlineStr"/>
       <c r="U79" s="8" t="inlineStr"/>
       <c r="V79" s="8" t="inlineStr"/>
+      <c r="W79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -8125,31 +8325,32 @@
           <t>+27 11 719 6300</t>
         </is>
       </c>
-      <c r="N80" s="7" t="inlineStr">
+      <c r="N80" s="7" t="inlineStr"/>
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="O80" s="7" t="inlineStr">
+      <c r="P80" s="7" t="inlineStr">
         <is>
           <t>packaging &amp; containers</t>
         </is>
       </c>
-      <c r="P80" s="7" t="inlineStr">
+      <c r="Q80" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q80" s="7" t="inlineStr">
+      <c r="R80" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R80" s="7" t="inlineStr"/>
-      <c r="S80" s="8" t="inlineStr"/>
+      <c r="S80" s="7" t="inlineStr"/>
       <c r="T80" s="8" t="inlineStr"/>
       <c r="U80" s="8" t="inlineStr"/>
       <c r="V80" s="8" t="inlineStr"/>
+      <c r="W80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -8213,31 +8414,32 @@
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr"/>
-      <c r="N81" s="7" t="inlineStr">
+      <c r="N81" s="7" t="inlineStr"/>
+      <c r="O81" s="7" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="O81" s="7" t="inlineStr">
+      <c r="P81" s="7" t="inlineStr">
         <is>
           <t>packaging &amp; containers</t>
         </is>
       </c>
-      <c r="P81" s="7" t="inlineStr">
+      <c r="Q81" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q81" s="7" t="inlineStr">
+      <c r="R81" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R81" s="7" t="inlineStr"/>
-      <c r="S81" s="8" t="inlineStr"/>
+      <c r="S81" s="7" t="inlineStr"/>
       <c r="T81" s="8" t="inlineStr"/>
       <c r="U81" s="8" t="inlineStr"/>
       <c r="V81" s="8" t="inlineStr"/>
+      <c r="W81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
@@ -8303,29 +8505,34 @@
       <c r="M82" s="7" t="inlineStr"/>
       <c r="N82" s="7" t="inlineStr">
         <is>
+          <t>+234 812 900 8457</t>
+        </is>
+      </c>
+      <c r="O82" s="7" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="O82" s="7" t="inlineStr">
+      <c r="P82" s="7" t="inlineStr">
         <is>
           <t>packaging &amp; containers</t>
         </is>
       </c>
-      <c r="P82" s="7" t="inlineStr">
+      <c r="Q82" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q82" s="7" t="inlineStr">
+      <c r="R82" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R82" s="7" t="inlineStr"/>
-      <c r="S82" s="8" t="inlineStr"/>
+      <c r="S82" s="7" t="inlineStr"/>
       <c r="T82" s="8" t="inlineStr"/>
       <c r="U82" s="8" t="inlineStr"/>
       <c r="V82" s="8" t="inlineStr"/>
+      <c r="W82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -8393,31 +8600,32 @@
           <t>+971 4 422 0720</t>
         </is>
       </c>
-      <c r="N83" s="7" t="inlineStr">
+      <c r="N83" s="7" t="inlineStr"/>
+      <c r="O83" s="7" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="O83" s="7" t="inlineStr">
+      <c r="P83" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P83" s="7" t="inlineStr">
+      <c r="Q83" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q83" s="7" t="inlineStr">
+      <c r="R83" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R83" s="7" t="inlineStr"/>
-      <c r="S83" s="8" t="inlineStr"/>
+      <c r="S83" s="7" t="inlineStr"/>
       <c r="T83" s="8" t="inlineStr"/>
       <c r="U83" s="8" t="inlineStr"/>
       <c r="V83" s="8" t="inlineStr"/>
+      <c r="W83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -8485,31 +8693,32 @@
           <t>+1 312-335-0245</t>
         </is>
       </c>
-      <c r="N84" s="7" t="inlineStr">
+      <c r="N84" s="7" t="inlineStr"/>
+      <c r="O84" s="7" t="inlineStr">
         <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="O84" s="7" t="inlineStr">
+      <c r="P84" s="7" t="inlineStr">
         <is>
           <t>plastics</t>
         </is>
       </c>
-      <c r="P84" s="7" t="inlineStr">
+      <c r="Q84" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q84" s="7" t="inlineStr">
+      <c r="R84" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R84" s="7" t="inlineStr"/>
-      <c r="S84" s="8" t="inlineStr"/>
+      <c r="S84" s="7" t="inlineStr"/>
       <c r="T84" s="8" t="inlineStr"/>
       <c r="U84" s="8" t="inlineStr"/>
       <c r="V84" s="8" t="inlineStr"/>
+      <c r="W84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -8579,29 +8788,34 @@
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
+          <t>+234 812 945 9570</t>
+        </is>
+      </c>
+      <c r="O85" s="7" t="inlineStr">
+        <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="O85" s="7" t="inlineStr">
+      <c r="P85" s="7" t="inlineStr">
         <is>
           <t>plastics</t>
         </is>
       </c>
-      <c r="P85" s="7" t="inlineStr">
+      <c r="Q85" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q85" s="7" t="inlineStr">
+      <c r="R85" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R85" s="7" t="inlineStr"/>
-      <c r="S85" s="8" t="inlineStr"/>
+      <c r="S85" s="7" t="inlineStr"/>
       <c r="T85" s="8" t="inlineStr"/>
       <c r="U85" s="8" t="inlineStr"/>
       <c r="V85" s="8" t="inlineStr"/>
+      <c r="W85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
@@ -8671,29 +8885,34 @@
       </c>
       <c r="N86" s="7" t="inlineStr">
         <is>
+          <t>+234 803 064 0402</t>
+        </is>
+      </c>
+      <c r="O86" s="7" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="O86" s="7" t="inlineStr">
+      <c r="P86" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P86" s="7" t="inlineStr">
+      <c r="Q86" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q86" s="7" t="inlineStr">
+      <c r="R86" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R86" s="7" t="inlineStr"/>
-      <c r="S86" s="8" t="inlineStr"/>
+      <c r="S86" s="7" t="inlineStr"/>
       <c r="T86" s="8" t="inlineStr"/>
       <c r="U86" s="8" t="inlineStr"/>
       <c r="V86" s="8" t="inlineStr"/>
+      <c r="W86" s="8" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -8761,31 +8980,32 @@
           <t>+234 812 343 8237</t>
         </is>
       </c>
-      <c r="N87" s="7" t="inlineStr">
+      <c r="N87" s="7" t="inlineStr"/>
+      <c r="O87" s="7" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="O87" s="7" t="inlineStr">
+      <c r="P87" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P87" s="7" t="inlineStr">
+      <c r="Q87" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q87" s="7" t="inlineStr">
+      <c r="R87" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R87" s="7" t="inlineStr"/>
-      <c r="S87" s="8" t="inlineStr"/>
+      <c r="S87" s="7" t="inlineStr"/>
       <c r="T87" s="8" t="inlineStr"/>
       <c r="U87" s="8" t="inlineStr"/>
       <c r="V87" s="8" t="inlineStr"/>
+      <c r="W87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -8853,31 +9073,32 @@
           <t>+234 810 216 4586</t>
         </is>
       </c>
-      <c r="N88" s="7" t="inlineStr">
+      <c r="N88" s="7" t="inlineStr"/>
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>370</t>
         </is>
       </c>
-      <c r="O88" s="7" t="inlineStr">
+      <c r="P88" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P88" s="7" t="inlineStr">
+      <c r="Q88" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q88" s="7" t="inlineStr">
+      <c r="R88" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R88" s="7" t="inlineStr"/>
-      <c r="S88" s="8" t="inlineStr"/>
+      <c r="S88" s="7" t="inlineStr"/>
       <c r="T88" s="8" t="inlineStr"/>
       <c r="U88" s="8" t="inlineStr"/>
       <c r="V88" s="8" t="inlineStr"/>
+      <c r="W88" s="8" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -8947,33 +9168,38 @@
       </c>
       <c r="N89" s="7" t="inlineStr">
         <is>
+          <t>+234 816 681 5635</t>
+        </is>
+      </c>
+      <c r="O89" s="7" t="inlineStr">
+        <is>
           <t>800</t>
         </is>
       </c>
-      <c r="O89" s="7" t="inlineStr">
+      <c r="P89" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P89" s="7" t="inlineStr">
+      <c r="Q89" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q89" s="7" t="inlineStr">
+      <c r="R89" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R89" s="9" t="inlineStr">
+      <c r="S89" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S89" s="8" t="inlineStr"/>
       <c r="T89" s="8" t="inlineStr"/>
       <c r="U89" s="8" t="inlineStr"/>
       <c r="V89" s="8" t="inlineStr"/>
+      <c r="W89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
@@ -9041,31 +9267,32 @@
           <t>+234 907 599 9096</t>
         </is>
       </c>
-      <c r="N90" s="7" t="inlineStr">
+      <c r="N90" s="7" t="inlineStr"/>
+      <c r="O90" s="7" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="O90" s="7" t="inlineStr">
+      <c r="P90" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P90" s="7" t="inlineStr">
+      <c r="Q90" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q90" s="7" t="inlineStr">
+      <c r="R90" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R90" s="7" t="inlineStr"/>
-      <c r="S90" s="8" t="inlineStr"/>
+      <c r="S90" s="7" t="inlineStr"/>
       <c r="T90" s="8" t="inlineStr"/>
       <c r="U90" s="8" t="inlineStr"/>
       <c r="V90" s="8" t="inlineStr"/>
+      <c r="W90" s="8" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -9133,31 +9360,32 @@
           <t>+1 262-260-2000</t>
         </is>
       </c>
-      <c r="N91" s="7" t="inlineStr">
+      <c r="N91" s="7" t="inlineStr"/>
+      <c r="O91" s="7" t="inlineStr">
         <is>
           <t>13000</t>
         </is>
       </c>
-      <c r="O91" s="7" t="inlineStr">
+      <c r="P91" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P91" s="7" t="inlineStr">
+      <c r="Q91" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q91" s="7" t="inlineStr">
+      <c r="R91" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R91" s="7" t="inlineStr"/>
-      <c r="S91" s="8" t="inlineStr"/>
+      <c r="S91" s="7" t="inlineStr"/>
       <c r="T91" s="8" t="inlineStr"/>
       <c r="U91" s="8" t="inlineStr"/>
       <c r="V91" s="8" t="inlineStr"/>
+      <c r="W91" s="8" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -9227,29 +9455,34 @@
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
+          <t>+91 95013 27345</t>
+        </is>
+      </c>
+      <c r="O92" s="7" t="inlineStr">
+        <is>
           <t>13000</t>
         </is>
       </c>
-      <c r="O92" s="7" t="inlineStr">
+      <c r="P92" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P92" s="7" t="inlineStr">
+      <c r="Q92" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q92" s="7" t="inlineStr">
+      <c r="R92" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R92" s="7" t="inlineStr"/>
-      <c r="S92" s="8" t="inlineStr"/>
+      <c r="S92" s="7" t="inlineStr"/>
       <c r="T92" s="8" t="inlineStr"/>
       <c r="U92" s="8" t="inlineStr"/>
       <c r="V92" s="8" t="inlineStr"/>
+      <c r="W92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -9317,31 +9550,32 @@
           <t>+1 812-945-1964</t>
         </is>
       </c>
-      <c r="N93" s="7" t="inlineStr">
+      <c r="N93" s="7" t="inlineStr"/>
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="O93" s="7" t="inlineStr">
+      <c r="P93" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P93" s="7" t="inlineStr">
+      <c r="Q93" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q93" s="7" t="inlineStr">
+      <c r="R93" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R93" s="7" t="inlineStr"/>
-      <c r="S93" s="8" t="inlineStr"/>
+      <c r="S93" s="7" t="inlineStr"/>
       <c r="T93" s="8" t="inlineStr"/>
       <c r="U93" s="8" t="inlineStr"/>
       <c r="V93" s="8" t="inlineStr"/>
+      <c r="W93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
@@ -9409,31 +9643,32 @@
           <t>+1 812-945-1964</t>
         </is>
       </c>
-      <c r="N94" s="7" t="inlineStr">
+      <c r="N94" s="7" t="inlineStr"/>
+      <c r="O94" s="7" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="O94" s="7" t="inlineStr">
+      <c r="P94" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P94" s="7" t="inlineStr">
+      <c r="Q94" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q94" s="7" t="inlineStr">
+      <c r="R94" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R94" s="7" t="inlineStr"/>
-      <c r="S94" s="8" t="inlineStr"/>
+      <c r="S94" s="7" t="inlineStr"/>
       <c r="T94" s="8" t="inlineStr"/>
       <c r="U94" s="8" t="inlineStr"/>
       <c r="V94" s="8" t="inlineStr"/>
+      <c r="W94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
@@ -9501,31 +9736,32 @@
           <t>+234 1 903 3905</t>
         </is>
       </c>
-      <c r="N95" s="7" t="inlineStr">
+      <c r="N95" s="7" t="inlineStr"/>
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>750</t>
         </is>
       </c>
-      <c r="O95" s="7" t="inlineStr">
+      <c r="P95" s="7" t="inlineStr">
         <is>
           <t>packaging &amp; containers</t>
         </is>
       </c>
-      <c r="P95" s="7" t="inlineStr">
+      <c r="Q95" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q95" s="7" t="inlineStr">
+      <c r="R95" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R95" s="7" t="inlineStr"/>
-      <c r="S95" s="8" t="inlineStr"/>
+      <c r="S95" s="7" t="inlineStr"/>
       <c r="T95" s="8" t="inlineStr"/>
       <c r="U95" s="8" t="inlineStr"/>
       <c r="V95" s="8" t="inlineStr"/>
+      <c r="W95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
@@ -9589,31 +9825,32 @@
         </is>
       </c>
       <c r="M96" s="7" t="inlineStr"/>
-      <c r="N96" s="7" t="inlineStr">
+      <c r="N96" s="7" t="inlineStr"/>
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="O96" s="7" t="inlineStr">
+      <c r="P96" s="7" t="inlineStr">
         <is>
           <t>automotive</t>
         </is>
       </c>
-      <c r="P96" s="7" t="inlineStr">
+      <c r="Q96" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q96" s="7" t="inlineStr">
+      <c r="R96" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R96" s="7" t="inlineStr"/>
-      <c r="S96" s="8" t="inlineStr"/>
+      <c r="S96" s="7" t="inlineStr"/>
       <c r="T96" s="8" t="inlineStr"/>
       <c r="U96" s="8" t="inlineStr"/>
       <c r="V96" s="8" t="inlineStr"/>
+      <c r="W96" s="8" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
@@ -9675,29 +9912,34 @@
       <c r="M97" s="7" t="inlineStr"/>
       <c r="N97" s="7" t="inlineStr">
         <is>
+          <t>+1 773-712-0943</t>
+        </is>
+      </c>
+      <c r="O97" s="7" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="O97" s="7" t="inlineStr">
+      <c r="P97" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P97" s="7" t="inlineStr">
+      <c r="Q97" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q97" s="7" t="inlineStr">
+      <c r="R97" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R97" s="7" t="inlineStr"/>
-      <c r="S97" s="8" t="inlineStr"/>
+      <c r="S97" s="7" t="inlineStr"/>
       <c r="T97" s="8" t="inlineStr"/>
       <c r="U97" s="8" t="inlineStr"/>
       <c r="V97" s="8" t="inlineStr"/>
+      <c r="W97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -9765,31 +10007,32 @@
           <t>+234 1 461 2476</t>
         </is>
       </c>
-      <c r="N98" s="7" t="inlineStr">
+      <c r="N98" s="7" t="inlineStr"/>
+      <c r="O98" s="7" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="O98" s="7" t="inlineStr">
+      <c r="P98" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P98" s="7" t="inlineStr">
+      <c r="Q98" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q98" s="7" t="inlineStr">
+      <c r="R98" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R98" s="7" t="inlineStr"/>
-      <c r="S98" s="8" t="inlineStr"/>
+      <c r="S98" s="7" t="inlineStr"/>
       <c r="T98" s="8" t="inlineStr"/>
       <c r="U98" s="8" t="inlineStr"/>
       <c r="V98" s="8" t="inlineStr"/>
+      <c r="W98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -9857,31 +10100,32 @@
           <t>+234 908 469 7959</t>
         </is>
       </c>
-      <c r="N99" s="7" t="inlineStr">
+      <c r="N99" s="7" t="inlineStr"/>
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="O99" s="7" t="inlineStr">
+      <c r="P99" s="7" t="inlineStr">
         <is>
           <t>packaging &amp; containers</t>
         </is>
       </c>
-      <c r="P99" s="7" t="inlineStr">
+      <c r="Q99" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q99" s="7" t="inlineStr">
+      <c r="R99" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R99" s="7" t="inlineStr"/>
-      <c r="S99" s="8" t="inlineStr"/>
+      <c r="S99" s="7" t="inlineStr"/>
       <c r="T99" s="8" t="inlineStr"/>
       <c r="U99" s="8" t="inlineStr"/>
       <c r="V99" s="8" t="inlineStr"/>
+      <c r="W99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
@@ -9945,31 +10189,32 @@
           <t>+46 46 287 33 00</t>
         </is>
       </c>
-      <c r="N100" s="7" t="inlineStr">
+      <c r="N100" s="7" t="inlineStr"/>
+      <c r="O100" s="7" t="inlineStr">
         <is>
           <t>170</t>
         </is>
       </c>
-      <c r="O100" s="7" t="inlineStr">
+      <c r="P100" s="7" t="inlineStr">
         <is>
           <t>packaging &amp; containers</t>
         </is>
       </c>
-      <c r="P100" s="7" t="inlineStr">
+      <c r="Q100" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q100" s="7" t="inlineStr">
+      <c r="R100" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R100" s="7" t="inlineStr"/>
-      <c r="S100" s="8" t="inlineStr"/>
+      <c r="S100" s="7" t="inlineStr"/>
       <c r="T100" s="8" t="inlineStr"/>
       <c r="U100" s="8" t="inlineStr"/>
       <c r="V100" s="8" t="inlineStr"/>
+      <c r="W100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
@@ -10035,29 +10280,34 @@
       <c r="M101" s="7" t="inlineStr"/>
       <c r="N101" s="7" t="inlineStr">
         <is>
+          <t>+234 703 932 8820</t>
+        </is>
+      </c>
+      <c r="O101" s="7" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="O101" s="7" t="inlineStr">
+      <c r="P101" s="7" t="inlineStr">
         <is>
           <t>paper &amp; forest products</t>
         </is>
       </c>
-      <c r="P101" s="7" t="inlineStr">
+      <c r="Q101" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q101" s="7" t="inlineStr">
+      <c r="R101" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R101" s="7" t="inlineStr"/>
-      <c r="S101" s="8" t="inlineStr"/>
+      <c r="S101" s="7" t="inlineStr"/>
       <c r="T101" s="8" t="inlineStr"/>
       <c r="U101" s="8" t="inlineStr"/>
       <c r="V101" s="8" t="inlineStr"/>
+      <c r="W101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
@@ -10127,29 +10377,34 @@
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
+          <t>+234 815 277 9485</t>
+        </is>
+      </c>
+      <c r="O102" s="7" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="O102" s="7" t="inlineStr">
+      <c r="P102" s="7" t="inlineStr">
         <is>
           <t>packaging &amp; containers</t>
         </is>
       </c>
-      <c r="P102" s="7" t="inlineStr">
+      <c r="Q102" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q102" s="7" t="inlineStr">
+      <c r="R102" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R102" s="7" t="inlineStr"/>
-      <c r="S102" s="8" t="inlineStr"/>
+      <c r="S102" s="7" t="inlineStr"/>
       <c r="T102" s="8" t="inlineStr"/>
       <c r="U102" s="8" t="inlineStr"/>
       <c r="V102" s="8" t="inlineStr"/>
+      <c r="W102" s="8" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
@@ -10213,31 +10468,32 @@
         </is>
       </c>
       <c r="M103" s="7" t="inlineStr"/>
-      <c r="N103" s="7" t="inlineStr">
+      <c r="N103" s="7" t="inlineStr"/>
+      <c r="O103" s="7" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="O103" s="7" t="inlineStr">
+      <c r="P103" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P103" s="7" t="inlineStr">
+      <c r="Q103" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q103" s="7" t="inlineStr">
+      <c r="R103" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R103" s="7" t="inlineStr"/>
-      <c r="S103" s="8" t="inlineStr"/>
+      <c r="S103" s="7" t="inlineStr"/>
       <c r="T103" s="8" t="inlineStr"/>
       <c r="U103" s="8" t="inlineStr"/>
       <c r="V103" s="8" t="inlineStr"/>
+      <c r="W103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
@@ -10305,31 +10561,32 @@
           <t>+234 700 2255 63987</t>
         </is>
       </c>
-      <c r="N104" s="7" t="inlineStr">
+      <c r="N104" s="7" t="inlineStr"/>
+      <c r="O104" s="7" t="inlineStr">
         <is>
           <t>630</t>
         </is>
       </c>
-      <c r="O104" s="7" t="inlineStr">
+      <c r="P104" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P104" s="7" t="inlineStr">
+      <c r="Q104" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q104" s="7" t="inlineStr">
+      <c r="R104" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R104" s="7" t="inlineStr"/>
-      <c r="S104" s="8" t="inlineStr"/>
+      <c r="S104" s="7" t="inlineStr"/>
       <c r="T104" s="8" t="inlineStr"/>
       <c r="U104" s="8" t="inlineStr"/>
       <c r="V104" s="8" t="inlineStr"/>
+      <c r="W104" s="8" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -10397,31 +10654,32 @@
           <t>+234 816 911 0000</t>
         </is>
       </c>
-      <c r="N105" s="7" t="inlineStr">
+      <c r="N105" s="7" t="inlineStr"/>
+      <c r="O105" s="7" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="O105" s="7" t="inlineStr">
+      <c r="P105" s="7" t="inlineStr">
         <is>
           <t>paper &amp; forest products</t>
         </is>
       </c>
-      <c r="P105" s="7" t="inlineStr">
+      <c r="Q105" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q105" s="7" t="inlineStr">
+      <c r="R105" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R105" s="7" t="inlineStr"/>
-      <c r="S105" s="8" t="inlineStr"/>
+      <c r="S105" s="7" t="inlineStr"/>
       <c r="T105" s="8" t="inlineStr"/>
       <c r="U105" s="8" t="inlineStr"/>
       <c r="V105" s="8" t="inlineStr"/>
+      <c r="W105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -10487,29 +10745,34 @@
       <c r="M106" s="7" t="inlineStr"/>
       <c r="N106" s="7" t="inlineStr">
         <is>
+          <t>+234 708 630 2523</t>
+        </is>
+      </c>
+      <c r="O106" s="7" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="O106" s="7" t="inlineStr">
+      <c r="P106" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P106" s="7" t="inlineStr">
+      <c r="Q106" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q106" s="7" t="inlineStr">
+      <c r="R106" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R106" s="7" t="inlineStr"/>
-      <c r="S106" s="8" t="inlineStr"/>
+      <c r="S106" s="7" t="inlineStr"/>
       <c r="T106" s="8" t="inlineStr"/>
       <c r="U106" s="8" t="inlineStr"/>
       <c r="V106" s="8" t="inlineStr"/>
+      <c r="W106" s="8" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
@@ -10577,31 +10840,32 @@
           <t>+234 810 612 2073</t>
         </is>
       </c>
-      <c r="N107" s="7" t="inlineStr">
+      <c r="N107" s="7" t="inlineStr"/>
+      <c r="O107" s="7" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O107" s="7" t="inlineStr">
+      <c r="P107" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P107" s="7" t="inlineStr">
+      <c r="Q107" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q107" s="7" t="inlineStr">
+      <c r="R107" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R107" s="7" t="inlineStr"/>
-      <c r="S107" s="8" t="inlineStr"/>
+      <c r="S107" s="7" t="inlineStr"/>
       <c r="T107" s="8" t="inlineStr"/>
       <c r="U107" s="8" t="inlineStr"/>
       <c r="V107" s="8" t="inlineStr"/>
+      <c r="W107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
@@ -10665,31 +10929,32 @@
         </is>
       </c>
       <c r="M108" s="7" t="inlineStr"/>
-      <c r="N108" s="7" t="inlineStr">
+      <c r="N108" s="7" t="inlineStr"/>
+      <c r="O108" s="7" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="O108" s="7" t="inlineStr">
+      <c r="P108" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P108" s="7" t="inlineStr">
+      <c r="Q108" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q108" s="7" t="inlineStr">
+      <c r="R108" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R108" s="7" t="inlineStr"/>
-      <c r="S108" s="8" t="inlineStr"/>
+      <c r="S108" s="7" t="inlineStr"/>
       <c r="T108" s="8" t="inlineStr"/>
       <c r="U108" s="8" t="inlineStr"/>
       <c r="V108" s="8" t="inlineStr"/>
+      <c r="W108" s="8" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
@@ -10757,31 +11022,32 @@
           <t>+234 700 33784 54973</t>
         </is>
       </c>
-      <c r="N109" s="7" t="inlineStr">
+      <c r="N109" s="7" t="inlineStr"/>
+      <c r="O109" s="7" t="inlineStr">
         <is>
           <t>390</t>
         </is>
       </c>
-      <c r="O109" s="7" t="inlineStr">
+      <c r="P109" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P109" s="7" t="inlineStr">
+      <c r="Q109" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q109" s="7" t="inlineStr">
+      <c r="R109" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R109" s="7" t="inlineStr"/>
-      <c r="S109" s="8" t="inlineStr"/>
+      <c r="S109" s="7" t="inlineStr"/>
       <c r="T109" s="8" t="inlineStr"/>
       <c r="U109" s="8" t="inlineStr"/>
       <c r="V109" s="8" t="inlineStr"/>
+      <c r="W109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
@@ -10849,31 +11115,32 @@
           <t>+234 1 460 5316</t>
         </is>
       </c>
-      <c r="N110" s="7" t="inlineStr">
+      <c r="N110" s="7" t="inlineStr"/>
+      <c r="O110" s="7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="O110" s="7" t="inlineStr">
+      <c r="P110" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P110" s="7" t="inlineStr">
+      <c r="Q110" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q110" s="7" t="inlineStr">
+      <c r="R110" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R110" s="7" t="inlineStr"/>
-      <c r="S110" s="8" t="inlineStr"/>
+      <c r="S110" s="7" t="inlineStr"/>
       <c r="T110" s="8" t="inlineStr"/>
       <c r="U110" s="8" t="inlineStr"/>
       <c r="V110" s="8" t="inlineStr"/>
+      <c r="W110" s="8" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
@@ -10943,29 +11210,34 @@
       </c>
       <c r="N111" s="7" t="inlineStr">
         <is>
+          <t>+234 703 236 6610</t>
+        </is>
+      </c>
+      <c r="O111" s="7" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="O111" s="7" t="inlineStr">
+      <c r="P111" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P111" s="7" t="inlineStr">
+      <c r="Q111" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q111" s="7" t="inlineStr">
+      <c r="R111" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R111" s="7" t="inlineStr"/>
-      <c r="S111" s="8" t="inlineStr"/>
+      <c r="S111" s="7" t="inlineStr"/>
       <c r="T111" s="8" t="inlineStr"/>
       <c r="U111" s="8" t="inlineStr"/>
       <c r="V111" s="8" t="inlineStr"/>
+      <c r="W111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -11031,29 +11303,34 @@
       <c r="M112" s="7" t="inlineStr"/>
       <c r="N112" s="7" t="inlineStr">
         <is>
+          <t>+92 333 8632738</t>
+        </is>
+      </c>
+      <c r="O112" s="7" t="inlineStr">
+        <is>
           <t>13000</t>
         </is>
       </c>
-      <c r="O112" s="7" t="inlineStr">
+      <c r="P112" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P112" s="7" t="inlineStr">
+      <c r="Q112" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q112" s="7" t="inlineStr">
+      <c r="R112" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R112" s="7" t="inlineStr"/>
-      <c r="S112" s="8" t="inlineStr"/>
+      <c r="S112" s="7" t="inlineStr"/>
       <c r="T112" s="8" t="inlineStr"/>
       <c r="U112" s="8" t="inlineStr"/>
       <c r="V112" s="8" t="inlineStr"/>
+      <c r="W112" s="8" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -11117,31 +11394,32 @@
         </is>
       </c>
       <c r="M113" s="7" t="inlineStr"/>
-      <c r="N113" s="7" t="inlineStr">
+      <c r="N113" s="7" t="inlineStr"/>
+      <c r="O113" s="7" t="inlineStr">
         <is>
           <t>13000</t>
         </is>
       </c>
-      <c r="O113" s="7" t="inlineStr">
+      <c r="P113" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P113" s="7" t="inlineStr">
+      <c r="Q113" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q113" s="7" t="inlineStr">
+      <c r="R113" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R113" s="7" t="inlineStr"/>
-      <c r="S113" s="8" t="inlineStr"/>
+      <c r="S113" s="7" t="inlineStr"/>
       <c r="T113" s="8" t="inlineStr"/>
       <c r="U113" s="8" t="inlineStr"/>
       <c r="V113" s="8" t="inlineStr"/>
+      <c r="W113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
@@ -11201,31 +11479,32 @@
         </is>
       </c>
       <c r="M114" s="7" t="inlineStr"/>
-      <c r="N114" s="7" t="inlineStr">
+      <c r="N114" s="7" t="inlineStr"/>
+      <c r="O114" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O114" s="7" t="inlineStr">
+      <c r="P114" s="7" t="inlineStr">
         <is>
           <t>plastics</t>
         </is>
       </c>
-      <c r="P114" s="7" t="inlineStr">
+      <c r="Q114" s="7" t="inlineStr">
         <is>
           <t>Critical spares second source on plant drives</t>
         </is>
       </c>
-      <c r="Q114" s="7" t="inlineStr">
+      <c r="R114" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R114" s="7" t="inlineStr"/>
-      <c r="S114" s="8" t="inlineStr"/>
+      <c r="S114" s="7" t="inlineStr"/>
       <c r="T114" s="8" t="inlineStr"/>
       <c r="U114" s="8" t="inlineStr"/>
       <c r="V114" s="8" t="inlineStr"/>
+      <c r="W114" s="8" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
@@ -11295,29 +11574,34 @@
       </c>
       <c r="N115" s="7" t="inlineStr">
         <is>
+          <t>+49 219 19072181</t>
+        </is>
+      </c>
+      <c r="O115" s="7" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="O115" s="7" t="inlineStr">
+      <c r="P115" s="7" t="inlineStr">
         <is>
           <t>wholesale</t>
         </is>
       </c>
-      <c r="P115" s="7" t="inlineStr">
+      <c r="Q115" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q115" s="7" t="inlineStr">
+      <c r="R115" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R115" s="7" t="inlineStr"/>
-      <c r="S115" s="8" t="inlineStr"/>
+      <c r="S115" s="7" t="inlineStr"/>
       <c r="T115" s="8" t="inlineStr"/>
       <c r="U115" s="8" t="inlineStr"/>
       <c r="V115" s="8" t="inlineStr"/>
+      <c r="W115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
@@ -11385,31 +11669,32 @@
           <t>+234 201 291 8597</t>
         </is>
       </c>
-      <c r="N116" s="7" t="inlineStr">
+      <c r="N116" s="7" t="inlineStr"/>
+      <c r="O116" s="7" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="O116" s="7" t="inlineStr">
+      <c r="P116" s="7" t="inlineStr">
         <is>
           <t>wholesale</t>
         </is>
       </c>
-      <c r="P116" s="7" t="inlineStr">
+      <c r="Q116" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q116" s="7" t="inlineStr">
+      <c r="R116" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R116" s="7" t="inlineStr"/>
-      <c r="S116" s="8" t="inlineStr"/>
+      <c r="S116" s="7" t="inlineStr"/>
       <c r="T116" s="8" t="inlineStr"/>
       <c r="U116" s="8" t="inlineStr"/>
       <c r="V116" s="8" t="inlineStr"/>
+      <c r="W116" s="8" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
@@ -11479,29 +11764,34 @@
       </c>
       <c r="N117" s="7" t="inlineStr">
         <is>
+          <t>+234 806 024 6164</t>
+        </is>
+      </c>
+      <c r="O117" s="7" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="O117" s="7" t="inlineStr">
+      <c r="P117" s="7" t="inlineStr">
         <is>
           <t>wholesale</t>
         </is>
       </c>
-      <c r="P117" s="7" t="inlineStr">
+      <c r="Q117" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q117" s="7" t="inlineStr">
+      <c r="R117" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R117" s="7" t="inlineStr"/>
-      <c r="S117" s="8" t="inlineStr"/>
+      <c r="S117" s="7" t="inlineStr"/>
       <c r="T117" s="8" t="inlineStr"/>
       <c r="U117" s="8" t="inlineStr"/>
       <c r="V117" s="8" t="inlineStr"/>
+      <c r="W117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
@@ -11571,29 +11861,34 @@
       </c>
       <c r="N118" s="7" t="inlineStr">
         <is>
+          <t>+234 805 611 9931</t>
+        </is>
+      </c>
+      <c r="O118" s="7" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="O118" s="7" t="inlineStr">
+      <c r="P118" s="7" t="inlineStr">
         <is>
           <t>wholesale</t>
         </is>
       </c>
-      <c r="P118" s="7" t="inlineStr">
+      <c r="Q118" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q118" s="7" t="inlineStr">
+      <c r="R118" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R118" s="7" t="inlineStr"/>
-      <c r="S118" s="8" t="inlineStr"/>
+      <c r="S118" s="7" t="inlineStr"/>
       <c r="T118" s="8" t="inlineStr"/>
       <c r="U118" s="8" t="inlineStr"/>
       <c r="V118" s="8" t="inlineStr"/>
+      <c r="W118" s="8" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -11661,31 +11956,32 @@
           <t>+234 201 291 8597</t>
         </is>
       </c>
-      <c r="N119" s="7" t="inlineStr">
+      <c r="N119" s="7" t="inlineStr"/>
+      <c r="O119" s="7" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="O119" s="7" t="inlineStr">
+      <c r="P119" s="7" t="inlineStr">
         <is>
           <t>wholesale</t>
         </is>
       </c>
-      <c r="P119" s="7" t="inlineStr">
+      <c r="Q119" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q119" s="7" t="inlineStr">
+      <c r="R119" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R119" s="7" t="inlineStr"/>
-      <c r="S119" s="8" t="inlineStr"/>
+      <c r="S119" s="7" t="inlineStr"/>
       <c r="T119" s="8" t="inlineStr"/>
       <c r="U119" s="8" t="inlineStr"/>
       <c r="V119" s="8" t="inlineStr"/>
+      <c r="W119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -11755,29 +12051,34 @@
       </c>
       <c r="N120" s="7" t="inlineStr">
         <is>
+          <t>+234 703 242 6471</t>
+        </is>
+      </c>
+      <c r="O120" s="7" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="O120" s="7" t="inlineStr">
+      <c r="P120" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P120" s="7" t="inlineStr">
+      <c r="Q120" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q120" s="7" t="inlineStr">
+      <c r="R120" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R120" s="7" t="inlineStr"/>
-      <c r="S120" s="8" t="inlineStr"/>
+      <c r="S120" s="7" t="inlineStr"/>
       <c r="T120" s="8" t="inlineStr"/>
       <c r="U120" s="8" t="inlineStr"/>
       <c r="V120" s="8" t="inlineStr"/>
+      <c r="W120" s="8" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
@@ -11845,31 +12146,32 @@
           <t>+234 806 231 3740</t>
         </is>
       </c>
-      <c r="N121" s="7" t="inlineStr">
+      <c r="N121" s="7" t="inlineStr"/>
+      <c r="O121" s="7" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="O121" s="7" t="inlineStr">
+      <c r="P121" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P121" s="7" t="inlineStr">
+      <c r="Q121" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q121" s="7" t="inlineStr">
+      <c r="R121" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R121" s="7" t="inlineStr"/>
-      <c r="S121" s="8" t="inlineStr"/>
+      <c r="S121" s="7" t="inlineStr"/>
       <c r="T121" s="8" t="inlineStr"/>
       <c r="U121" s="8" t="inlineStr"/>
       <c r="V121" s="8" t="inlineStr"/>
+      <c r="W121" s="8" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
@@ -11939,33 +12241,38 @@
       </c>
       <c r="N122" s="7" t="inlineStr">
         <is>
+          <t>+234 815 117 9255</t>
+        </is>
+      </c>
+      <c r="O122" s="7" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="O122" s="7" t="inlineStr">
+      <c r="P122" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P122" s="7" t="inlineStr">
+      <c r="Q122" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q122" s="7" t="inlineStr">
+      <c r="R122" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R122" s="9" t="inlineStr">
+      <c r="S122" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S122" s="8" t="inlineStr"/>
       <c r="T122" s="8" t="inlineStr"/>
       <c r="U122" s="8" t="inlineStr"/>
       <c r="V122" s="8" t="inlineStr"/>
+      <c r="W122" s="8" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
@@ -12033,35 +12340,36 @@
           <t>+234 701 821 9200</t>
         </is>
       </c>
-      <c r="N123" s="7" t="inlineStr">
+      <c r="N123" s="7" t="inlineStr"/>
+      <c r="O123" s="7" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="O123" s="7" t="inlineStr">
+      <c r="P123" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P123" s="7" t="inlineStr">
+      <c r="Q123" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q123" s="7" t="inlineStr">
+      <c r="R123" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R123" s="9" t="inlineStr">
+      <c r="S123" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S123" s="8" t="inlineStr"/>
       <c r="T123" s="8" t="inlineStr"/>
       <c r="U123" s="8" t="inlineStr"/>
       <c r="V123" s="8" t="inlineStr"/>
+      <c r="W123" s="8" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
@@ -12129,31 +12437,32 @@
           <t>+234 701 821 9200</t>
         </is>
       </c>
-      <c r="N124" s="7" t="inlineStr">
+      <c r="N124" s="7" t="inlineStr"/>
+      <c r="O124" s="7" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="O124" s="7" t="inlineStr">
+      <c r="P124" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P124" s="7" t="inlineStr">
+      <c r="Q124" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q124" s="7" t="inlineStr">
+      <c r="R124" s="7" t="inlineStr">
         <is>
           <t>Ms.</t>
         </is>
       </c>
-      <c r="R124" s="7" t="inlineStr"/>
-      <c r="S124" s="8" t="inlineStr"/>
+      <c r="S124" s="7" t="inlineStr"/>
       <c r="T124" s="8" t="inlineStr"/>
       <c r="U124" s="8" t="inlineStr"/>
       <c r="V124" s="8" t="inlineStr"/>
+      <c r="W124" s="8" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
@@ -12223,29 +12532,34 @@
       </c>
       <c r="N125" s="7" t="inlineStr">
         <is>
+          <t>+234 809 955 7924</t>
+        </is>
+      </c>
+      <c r="O125" s="7" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="O125" s="7" t="inlineStr">
+      <c r="P125" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P125" s="7" t="inlineStr">
+      <c r="Q125" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q125" s="7" t="inlineStr">
+      <c r="R125" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R125" s="7" t="inlineStr"/>
-      <c r="S125" s="8" t="inlineStr"/>
+      <c r="S125" s="7" t="inlineStr"/>
       <c r="T125" s="8" t="inlineStr"/>
       <c r="U125" s="8" t="inlineStr"/>
       <c r="V125" s="8" t="inlineStr"/>
+      <c r="W125" s="8" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -12315,29 +12629,34 @@
       </c>
       <c r="N126" s="7" t="inlineStr">
         <is>
+          <t>+234 802 810 5266</t>
+        </is>
+      </c>
+      <c r="O126" s="7" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="O126" s="7" t="inlineStr">
+      <c r="P126" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P126" s="7" t="inlineStr">
+      <c r="Q126" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q126" s="7" t="inlineStr">
+      <c r="R126" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R126" s="7" t="inlineStr"/>
-      <c r="S126" s="8" t="inlineStr"/>
+      <c r="S126" s="7" t="inlineStr"/>
       <c r="T126" s="8" t="inlineStr"/>
       <c r="U126" s="8" t="inlineStr"/>
       <c r="V126" s="8" t="inlineStr"/>
+      <c r="W126" s="8" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -12403,29 +12722,34 @@
       <c r="M127" s="7" t="inlineStr"/>
       <c r="N127" s="7" t="inlineStr">
         <is>
+          <t>+234 803 402 1158</t>
+        </is>
+      </c>
+      <c r="O127" s="7" t="inlineStr">
+        <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="O127" s="7" t="inlineStr">
+      <c r="P127" s="7" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="P127" s="7" t="inlineStr">
+      <c r="Q127" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q127" s="7" t="inlineStr">
+      <c r="R127" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R127" s="7" t="inlineStr"/>
-      <c r="S127" s="8" t="inlineStr"/>
+      <c r="S127" s="7" t="inlineStr"/>
       <c r="T127" s="8" t="inlineStr"/>
       <c r="U127" s="8" t="inlineStr"/>
       <c r="V127" s="8" t="inlineStr"/>
+      <c r="W127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
@@ -12489,31 +12813,32 @@
         </is>
       </c>
       <c r="M128" s="7" t="inlineStr"/>
-      <c r="N128" s="7" t="inlineStr">
+      <c r="N128" s="7" t="inlineStr"/>
+      <c r="O128" s="7" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="O128" s="7" t="inlineStr">
+      <c r="P128" s="7" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="P128" s="7" t="inlineStr">
+      <c r="Q128" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q128" s="7" t="inlineStr">
+      <c r="R128" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R128" s="7" t="inlineStr"/>
-      <c r="S128" s="8" t="inlineStr"/>
+      <c r="S128" s="7" t="inlineStr"/>
       <c r="T128" s="8" t="inlineStr"/>
       <c r="U128" s="8" t="inlineStr"/>
       <c r="V128" s="8" t="inlineStr"/>
+      <c r="W128" s="8" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
@@ -12577,31 +12902,32 @@
         </is>
       </c>
       <c r="M129" s="7" t="inlineStr"/>
-      <c r="N129" s="7" t="inlineStr">
+      <c r="N129" s="7" t="inlineStr"/>
+      <c r="O129" s="7" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="O129" s="7" t="inlineStr">
+      <c r="P129" s="7" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="P129" s="7" t="inlineStr">
+      <c r="Q129" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q129" s="7" t="inlineStr">
+      <c r="R129" s="7" t="inlineStr">
         <is>
           <t>Ms.</t>
         </is>
       </c>
-      <c r="R129" s="7" t="inlineStr"/>
-      <c r="S129" s="8" t="inlineStr"/>
+      <c r="S129" s="7" t="inlineStr"/>
       <c r="T129" s="8" t="inlineStr"/>
       <c r="U129" s="8" t="inlineStr"/>
       <c r="V129" s="8" t="inlineStr"/>
+      <c r="W129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
@@ -12665,31 +12991,32 @@
         </is>
       </c>
       <c r="M130" s="7" t="inlineStr"/>
-      <c r="N130" s="7" t="inlineStr">
+      <c r="N130" s="7" t="inlineStr"/>
+      <c r="O130" s="7" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="O130" s="7" t="inlineStr">
+      <c r="P130" s="7" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="P130" s="7" t="inlineStr">
+      <c r="Q130" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q130" s="7" t="inlineStr">
+      <c r="R130" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R130" s="7" t="inlineStr"/>
-      <c r="S130" s="8" t="inlineStr"/>
+      <c r="S130" s="7" t="inlineStr"/>
       <c r="T130" s="8" t="inlineStr"/>
       <c r="U130" s="8" t="inlineStr"/>
       <c r="V130" s="8" t="inlineStr"/>
+      <c r="W130" s="8" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
@@ -12759,33 +13086,38 @@
       </c>
       <c r="N131" s="7" t="inlineStr">
         <is>
+          <t>+234 802 305 6928</t>
+        </is>
+      </c>
+      <c r="O131" s="7" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="O131" s="7" t="inlineStr">
+      <c r="P131" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P131" s="7" t="inlineStr">
+      <c r="Q131" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q131" s="7" t="inlineStr">
+      <c r="R131" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R131" s="9" t="inlineStr">
+      <c r="S131" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S131" s="8" t="inlineStr"/>
       <c r="T131" s="8" t="inlineStr"/>
       <c r="U131" s="8" t="inlineStr"/>
       <c r="V131" s="8" t="inlineStr"/>
+      <c r="W131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
@@ -12853,31 +13185,32 @@
           <t>+234 803 332 2695</t>
         </is>
       </c>
-      <c r="N132" s="7" t="inlineStr">
+      <c r="N132" s="7" t="inlineStr"/>
+      <c r="O132" s="7" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="O132" s="7" t="inlineStr">
+      <c r="P132" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P132" s="7" t="inlineStr">
+      <c r="Q132" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q132" s="7" t="inlineStr">
+      <c r="R132" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R132" s="7" t="inlineStr"/>
-      <c r="S132" s="8" t="inlineStr"/>
+      <c r="S132" s="7" t="inlineStr"/>
       <c r="T132" s="8" t="inlineStr"/>
       <c r="U132" s="8" t="inlineStr"/>
       <c r="V132" s="8" t="inlineStr"/>
+      <c r="W132" s="8" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -12947,33 +13280,38 @@
       </c>
       <c r="N133" s="7" t="inlineStr">
         <is>
+          <t>+234 803 673 2280</t>
+        </is>
+      </c>
+      <c r="O133" s="7" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="O133" s="7" t="inlineStr">
+      <c r="P133" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P133" s="7" t="inlineStr">
+      <c r="Q133" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q133" s="7" t="inlineStr">
+      <c r="R133" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R133" s="9" t="inlineStr">
+      <c r="S133" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S133" s="8" t="inlineStr"/>
       <c r="T133" s="8" t="inlineStr"/>
       <c r="U133" s="8" t="inlineStr"/>
       <c r="V133" s="8" t="inlineStr"/>
+      <c r="W133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -13041,31 +13379,32 @@
           <t>+234 812 005 0716</t>
         </is>
       </c>
-      <c r="N134" s="7" t="inlineStr">
+      <c r="N134" s="7" t="inlineStr"/>
+      <c r="O134" s="7" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="O134" s="7" t="inlineStr">
+      <c r="P134" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P134" s="7" t="inlineStr">
+      <c r="Q134" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q134" s="7" t="inlineStr">
+      <c r="R134" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R134" s="7" t="inlineStr"/>
-      <c r="S134" s="8" t="inlineStr"/>
+      <c r="S134" s="7" t="inlineStr"/>
       <c r="T134" s="8" t="inlineStr"/>
       <c r="U134" s="8" t="inlineStr"/>
       <c r="V134" s="8" t="inlineStr"/>
+      <c r="W134" s="8" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
@@ -13135,29 +13474,34 @@
       </c>
       <c r="N135" s="7" t="inlineStr">
         <is>
+          <t>+234 703 037 0687</t>
+        </is>
+      </c>
+      <c r="O135" s="7" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="O135" s="7" t="inlineStr">
+      <c r="P135" s="7" t="inlineStr">
         <is>
           <t>information technology &amp; services</t>
         </is>
       </c>
-      <c r="P135" s="7" t="inlineStr">
+      <c r="Q135" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q135" s="7" t="inlineStr">
+      <c r="R135" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R135" s="7" t="inlineStr"/>
-      <c r="S135" s="8" t="inlineStr"/>
+      <c r="S135" s="7" t="inlineStr"/>
       <c r="T135" s="8" t="inlineStr"/>
       <c r="U135" s="8" t="inlineStr"/>
       <c r="V135" s="8" t="inlineStr"/>
+      <c r="W135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
@@ -13225,35 +13569,36 @@
           <t>+234 905 551 1862</t>
         </is>
       </c>
-      <c r="N136" s="7" t="inlineStr">
+      <c r="N136" s="7" t="inlineStr"/>
+      <c r="O136" s="7" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="O136" s="7" t="inlineStr">
+      <c r="P136" s="7" t="inlineStr">
         <is>
           <t>information technology &amp; services</t>
         </is>
       </c>
-      <c r="P136" s="7" t="inlineStr">
+      <c r="Q136" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q136" s="7" t="inlineStr">
+      <c r="R136" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R136" s="9" t="inlineStr">
+      <c r="S136" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S136" s="8" t="inlineStr"/>
       <c r="T136" s="8" t="inlineStr"/>
       <c r="U136" s="8" t="inlineStr"/>
       <c r="V136" s="8" t="inlineStr"/>
+      <c r="W136" s="8" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
@@ -13321,31 +13666,32 @@
           <t>+234 905 551 1862</t>
         </is>
       </c>
-      <c r="N137" s="7" t="inlineStr">
+      <c r="N137" s="7" t="inlineStr"/>
+      <c r="O137" s="7" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="O137" s="7" t="inlineStr">
+      <c r="P137" s="7" t="inlineStr">
         <is>
           <t>information technology &amp; services</t>
         </is>
       </c>
-      <c r="P137" s="7" t="inlineStr">
+      <c r="Q137" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q137" s="7" t="inlineStr">
+      <c r="R137" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R137" s="7" t="inlineStr"/>
-      <c r="S137" s="8" t="inlineStr"/>
+      <c r="S137" s="7" t="inlineStr"/>
       <c r="T137" s="8" t="inlineStr"/>
       <c r="U137" s="8" t="inlineStr"/>
       <c r="V137" s="8" t="inlineStr"/>
+      <c r="W137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
@@ -13413,31 +13759,32 @@
           <t>+44 1279 652776</t>
         </is>
       </c>
-      <c r="N138" s="7" t="inlineStr">
+      <c r="N138" s="7" t="inlineStr"/>
+      <c r="O138" s="7" t="inlineStr">
         <is>
           <t>1700</t>
         </is>
       </c>
-      <c r="O138" s="7" t="inlineStr">
+      <c r="P138" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P138" s="7" t="inlineStr">
+      <c r="Q138" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q138" s="7" t="inlineStr">
+      <c r="R138" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R138" s="7" t="inlineStr"/>
-      <c r="S138" s="8" t="inlineStr"/>
+      <c r="S138" s="7" t="inlineStr"/>
       <c r="T138" s="8" t="inlineStr"/>
       <c r="U138" s="8" t="inlineStr"/>
       <c r="V138" s="8" t="inlineStr"/>
+      <c r="W138" s="8" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
@@ -13507,29 +13854,34 @@
       </c>
       <c r="N139" s="7" t="inlineStr">
         <is>
+          <t>+234 803 328 3840</t>
+        </is>
+      </c>
+      <c r="O139" s="7" t="inlineStr">
+        <is>
           <t>14000</t>
         </is>
       </c>
-      <c r="O139" s="7" t="inlineStr">
+      <c r="P139" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P139" s="7" t="inlineStr">
+      <c r="Q139" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q139" s="7" t="inlineStr">
+      <c r="R139" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R139" s="7" t="inlineStr"/>
-      <c r="S139" s="8" t="inlineStr"/>
+      <c r="S139" s="7" t="inlineStr"/>
       <c r="T139" s="8" t="inlineStr"/>
       <c r="U139" s="8" t="inlineStr"/>
       <c r="V139" s="8" t="inlineStr"/>
+      <c r="W139" s="8" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
@@ -13597,31 +13949,32 @@
           <t>+41 52 262 30 00</t>
         </is>
       </c>
-      <c r="N140" s="7" t="inlineStr">
+      <c r="N140" s="7" t="inlineStr"/>
+      <c r="O140" s="7" t="inlineStr">
         <is>
           <t>14000</t>
         </is>
       </c>
-      <c r="O140" s="7" t="inlineStr">
+      <c r="P140" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P140" s="7" t="inlineStr">
+      <c r="Q140" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q140" s="7" t="inlineStr">
+      <c r="R140" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R140" s="7" t="inlineStr"/>
-      <c r="S140" s="8" t="inlineStr"/>
+      <c r="S140" s="7" t="inlineStr"/>
       <c r="T140" s="8" t="inlineStr"/>
       <c r="U140" s="8" t="inlineStr"/>
       <c r="V140" s="8" t="inlineStr"/>
+      <c r="W140" s="8" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
@@ -13689,31 +14042,32 @@
           <t>+234 803 320 7819</t>
         </is>
       </c>
-      <c r="N141" s="7" t="inlineStr">
+      <c r="N141" s="7" t="inlineStr"/>
+      <c r="O141" s="7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="O141" s="7" t="inlineStr">
+      <c r="P141" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P141" s="7" t="inlineStr">
+      <c r="Q141" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q141" s="7" t="inlineStr">
+      <c r="R141" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R141" s="7" t="inlineStr"/>
-      <c r="S141" s="8" t="inlineStr"/>
+      <c r="S141" s="7" t="inlineStr"/>
       <c r="T141" s="8" t="inlineStr"/>
       <c r="U141" s="8" t="inlineStr"/>
       <c r="V141" s="8" t="inlineStr"/>
+      <c r="W141" s="8" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
@@ -13783,29 +14137,34 @@
       </c>
       <c r="N142" s="7" t="inlineStr">
         <is>
+          <t>+234 803 359 6326</t>
+        </is>
+      </c>
+      <c r="O142" s="7" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O142" s="7" t="inlineStr">
+      <c r="P142" s="7" t="inlineStr">
         <is>
           <t>information technology &amp; services</t>
         </is>
       </c>
-      <c r="P142" s="7" t="inlineStr">
+      <c r="Q142" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q142" s="7" t="inlineStr">
+      <c r="R142" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R142" s="7" t="inlineStr"/>
-      <c r="S142" s="8" t="inlineStr"/>
+      <c r="S142" s="7" t="inlineStr"/>
       <c r="T142" s="8" t="inlineStr"/>
       <c r="U142" s="8" t="inlineStr"/>
       <c r="V142" s="8" t="inlineStr"/>
+      <c r="W142" s="8" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
@@ -13873,31 +14232,32 @@
           <t>+234 813 233 2330</t>
         </is>
       </c>
-      <c r="N143" s="7" t="inlineStr">
+      <c r="N143" s="7" t="inlineStr"/>
+      <c r="O143" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O143" s="7" t="inlineStr">
+      <c r="P143" s="7" t="inlineStr">
         <is>
           <t>information technology &amp; services</t>
         </is>
       </c>
-      <c r="P143" s="7" t="inlineStr">
+      <c r="Q143" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q143" s="7" t="inlineStr">
+      <c r="R143" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R143" s="7" t="inlineStr"/>
-      <c r="S143" s="8" t="inlineStr"/>
+      <c r="S143" s="7" t="inlineStr"/>
       <c r="T143" s="8" t="inlineStr"/>
       <c r="U143" s="8" t="inlineStr"/>
       <c r="V143" s="8" t="inlineStr"/>
+      <c r="W143" s="8" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
@@ -13959,29 +14319,34 @@
       <c r="M144" s="7" t="inlineStr"/>
       <c r="N144" s="7" t="inlineStr">
         <is>
+          <t>+234 903 738 0009</t>
+        </is>
+      </c>
+      <c r="O144" s="7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O144" s="7" t="inlineStr">
+      <c r="P144" s="7" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="P144" s="7" t="inlineStr">
+      <c r="Q144" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q144" s="7" t="inlineStr">
+      <c r="R144" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R144" s="7" t="inlineStr"/>
-      <c r="S144" s="8" t="inlineStr"/>
+      <c r="S144" s="7" t="inlineStr"/>
       <c r="T144" s="8" t="inlineStr"/>
       <c r="U144" s="8" t="inlineStr"/>
       <c r="V144" s="8" t="inlineStr"/>
+      <c r="W144" s="8" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
@@ -14051,29 +14416,34 @@
       </c>
       <c r="N145" s="7" t="inlineStr">
         <is>
+          <t>+91 99357 45999</t>
+        </is>
+      </c>
+      <c r="O145" s="7" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O145" s="7" t="inlineStr">
+      <c r="P145" s="7" t="inlineStr">
         <is>
           <t>civic &amp; social organization</t>
         </is>
       </c>
-      <c r="P145" s="7" t="inlineStr">
+      <c r="Q145" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q145" s="7" t="inlineStr">
+      <c r="R145" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R145" s="7" t="inlineStr"/>
-      <c r="S145" s="8" t="inlineStr"/>
+      <c r="S145" s="7" t="inlineStr"/>
       <c r="T145" s="8" t="inlineStr"/>
       <c r="U145" s="8" t="inlineStr"/>
       <c r="V145" s="8" t="inlineStr"/>
+      <c r="W145" s="8" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
@@ -14139,29 +14509,34 @@
       <c r="M146" s="7" t="inlineStr"/>
       <c r="N146" s="7" t="inlineStr">
         <is>
+          <t>+234 803 841 7362 / +234 908 550 2856</t>
+        </is>
+      </c>
+      <c r="O146" s="7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O146" s="7" t="inlineStr">
+      <c r="P146" s="7" t="inlineStr">
         <is>
           <t>logistics &amp; supply chain</t>
         </is>
       </c>
-      <c r="P146" s="7" t="inlineStr">
+      <c r="Q146" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q146" s="7" t="inlineStr">
+      <c r="R146" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R146" s="7" t="inlineStr"/>
-      <c r="S146" s="8" t="inlineStr"/>
+      <c r="S146" s="7" t="inlineStr"/>
       <c r="T146" s="8" t="inlineStr"/>
       <c r="U146" s="8" t="inlineStr"/>
       <c r="V146" s="8" t="inlineStr"/>
+      <c r="W146" s="8" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -14227,29 +14602,34 @@
       <c r="M147" s="7" t="inlineStr"/>
       <c r="N147" s="7" t="inlineStr">
         <is>
+          <t>+234 802 831 5141</t>
+        </is>
+      </c>
+      <c r="O147" s="7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O147" s="7" t="inlineStr">
+      <c r="P147" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P147" s="7" t="inlineStr">
+      <c r="Q147" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q147" s="7" t="inlineStr">
+      <c r="R147" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R147" s="7" t="inlineStr"/>
-      <c r="S147" s="8" t="inlineStr"/>
+      <c r="S147" s="7" t="inlineStr"/>
       <c r="T147" s="8" t="inlineStr"/>
       <c r="U147" s="8" t="inlineStr"/>
       <c r="V147" s="8" t="inlineStr"/>
+      <c r="W147" s="8" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -14319,29 +14699,34 @@
       </c>
       <c r="N148" s="7" t="inlineStr">
         <is>
+          <t>+234 704 565 6847</t>
+        </is>
+      </c>
+      <c r="O148" s="7" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="O148" s="7" t="inlineStr">
+      <c r="P148" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P148" s="7" t="inlineStr">
+      <c r="Q148" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q148" s="7" t="inlineStr">
+      <c r="R148" s="7" t="inlineStr">
         <is>
           <t>Ms.</t>
         </is>
       </c>
-      <c r="R148" s="7" t="inlineStr"/>
-      <c r="S148" s="8" t="inlineStr"/>
+      <c r="S148" s="7" t="inlineStr"/>
       <c r="T148" s="8" t="inlineStr"/>
       <c r="U148" s="8" t="inlineStr"/>
       <c r="V148" s="8" t="inlineStr"/>
+      <c r="W148" s="8" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
@@ -14411,29 +14796,34 @@
       </c>
       <c r="N149" s="7" t="inlineStr">
         <is>
+          <t>+91 97277 67085</t>
+        </is>
+      </c>
+      <c r="O149" s="7" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="O149" s="7" t="inlineStr">
+      <c r="P149" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P149" s="7" t="inlineStr">
+      <c r="Q149" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q149" s="7" t="inlineStr">
+      <c r="R149" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R149" s="7" t="inlineStr"/>
-      <c r="S149" s="8" t="inlineStr"/>
+      <c r="S149" s="7" t="inlineStr"/>
       <c r="T149" s="8" t="inlineStr"/>
       <c r="U149" s="8" t="inlineStr"/>
       <c r="V149" s="8" t="inlineStr"/>
+      <c r="W149" s="8" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
@@ -14503,29 +14893,34 @@
       </c>
       <c r="N150" s="7" t="inlineStr">
         <is>
+          <t>+91 97111 08133</t>
+        </is>
+      </c>
+      <c r="O150" s="7" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="O150" s="7" t="inlineStr">
+      <c r="P150" s="7" t="inlineStr">
         <is>
           <t>chemicals</t>
         </is>
       </c>
-      <c r="P150" s="7" t="inlineStr">
+      <c r="Q150" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q150" s="7" t="inlineStr">
+      <c r="R150" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R150" s="7" t="inlineStr"/>
-      <c r="S150" s="8" t="inlineStr"/>
+      <c r="S150" s="7" t="inlineStr"/>
       <c r="T150" s="8" t="inlineStr"/>
       <c r="U150" s="8" t="inlineStr"/>
       <c r="V150" s="8" t="inlineStr"/>
+      <c r="W150" s="8" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
@@ -14593,31 +14988,32 @@
           <t>+234 708 021 4561</t>
         </is>
       </c>
-      <c r="N151" s="7" t="inlineStr">
+      <c r="N151" s="7" t="inlineStr"/>
+      <c r="O151" s="7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O151" s="7" t="inlineStr">
+      <c r="P151" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P151" s="7" t="inlineStr">
+      <c r="Q151" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q151" s="7" t="inlineStr">
+      <c r="R151" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R151" s="7" t="inlineStr"/>
-      <c r="S151" s="8" t="inlineStr"/>
+      <c r="S151" s="7" t="inlineStr"/>
       <c r="T151" s="8" t="inlineStr"/>
       <c r="U151" s="8" t="inlineStr"/>
       <c r="V151" s="8" t="inlineStr"/>
+      <c r="W151" s="8" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
@@ -14685,31 +15081,32 @@
           <t>+353 1 812 9700</t>
         </is>
       </c>
-      <c r="N152" s="7" t="inlineStr">
+      <c r="N152" s="7" t="inlineStr"/>
+      <c r="O152" s="7" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="O152" s="7" t="inlineStr">
+      <c r="P152" s="7" t="inlineStr">
         <is>
           <t>farming</t>
         </is>
       </c>
-      <c r="P152" s="7" t="inlineStr">
+      <c r="Q152" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q152" s="7" t="inlineStr">
+      <c r="R152" s="7" t="inlineStr">
         <is>
           <t>Ms.</t>
         </is>
       </c>
-      <c r="R152" s="7" t="inlineStr"/>
-      <c r="S152" s="8" t="inlineStr"/>
+      <c r="S152" s="7" t="inlineStr"/>
       <c r="T152" s="8" t="inlineStr"/>
       <c r="U152" s="8" t="inlineStr"/>
       <c r="V152" s="8" t="inlineStr"/>
+      <c r="W152" s="8" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
@@ -14779,29 +15176,34 @@
       </c>
       <c r="N153" s="7" t="inlineStr">
         <is>
+          <t>+234 708 214 2510</t>
+        </is>
+      </c>
+      <c r="O153" s="7" t="inlineStr">
+        <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="O153" s="7" t="inlineStr">
+      <c r="P153" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P153" s="7" t="inlineStr">
+      <c r="Q153" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q153" s="7" t="inlineStr">
+      <c r="R153" s="7" t="inlineStr">
         <is>
           <t>Ms.</t>
         </is>
       </c>
-      <c r="R153" s="7" t="inlineStr"/>
-      <c r="S153" s="8" t="inlineStr"/>
+      <c r="S153" s="7" t="inlineStr"/>
       <c r="T153" s="8" t="inlineStr"/>
       <c r="U153" s="8" t="inlineStr"/>
       <c r="V153" s="8" t="inlineStr"/>
+      <c r="W153" s="8" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -14871,29 +15273,34 @@
       </c>
       <c r="N154" s="7" t="inlineStr">
         <is>
+          <t>+91 80874 52889</t>
+        </is>
+      </c>
+      <c r="O154" s="7" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="O154" s="7" t="inlineStr">
+      <c r="P154" s="7" t="inlineStr">
         <is>
           <t>import &amp; export</t>
         </is>
       </c>
-      <c r="P154" s="7" t="inlineStr">
+      <c r="Q154" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q154" s="7" t="inlineStr">
+      <c r="R154" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R154" s="7" t="inlineStr"/>
-      <c r="S154" s="8" t="inlineStr"/>
+      <c r="S154" s="7" t="inlineStr"/>
       <c r="T154" s="8" t="inlineStr"/>
       <c r="U154" s="8" t="inlineStr"/>
       <c r="V154" s="8" t="inlineStr"/>
+      <c r="W154" s="8" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -14963,29 +15370,34 @@
       </c>
       <c r="N155" s="7" t="inlineStr">
         <is>
+          <t>+234 708 869 5597</t>
+        </is>
+      </c>
+      <c r="O155" s="7" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O155" s="7" t="inlineStr">
+      <c r="P155" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P155" s="7" t="inlineStr">
+      <c r="Q155" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q155" s="7" t="inlineStr">
+      <c r="R155" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R155" s="7" t="inlineStr"/>
-      <c r="S155" s="8" t="inlineStr"/>
+      <c r="S155" s="7" t="inlineStr"/>
       <c r="T155" s="8" t="inlineStr"/>
       <c r="U155" s="8" t="inlineStr"/>
       <c r="V155" s="8" t="inlineStr"/>
+      <c r="W155" s="8" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
@@ -15053,31 +15465,32 @@
           <t>+234 803 407 0919</t>
         </is>
       </c>
-      <c r="N156" s="7" t="inlineStr">
+      <c r="N156" s="7" t="inlineStr"/>
+      <c r="O156" s="7" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="O156" s="7" t="inlineStr">
+      <c r="P156" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P156" s="7" t="inlineStr">
+      <c r="Q156" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q156" s="7" t="inlineStr">
+      <c r="R156" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R156" s="7" t="inlineStr"/>
-      <c r="S156" s="8" t="inlineStr"/>
+      <c r="S156" s="7" t="inlineStr"/>
       <c r="T156" s="8" t="inlineStr"/>
       <c r="U156" s="8" t="inlineStr"/>
       <c r="V156" s="8" t="inlineStr"/>
+      <c r="W156" s="8" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
@@ -15145,35 +15558,36 @@
           <t>+234 803 667 8281</t>
         </is>
       </c>
-      <c r="N157" s="7" t="inlineStr">
+      <c r="N157" s="7" t="inlineStr"/>
+      <c r="O157" s="7" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="O157" s="7" t="inlineStr">
+      <c r="P157" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P157" s="7" t="inlineStr">
+      <c r="Q157" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q157" s="7" t="inlineStr">
+      <c r="R157" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R157" s="9" t="inlineStr">
+      <c r="S157" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S157" s="8" t="inlineStr"/>
       <c r="T157" s="8" t="inlineStr"/>
       <c r="U157" s="8" t="inlineStr"/>
       <c r="V157" s="8" t="inlineStr"/>
+      <c r="W157" s="8" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
@@ -15235,29 +15649,34 @@
       <c r="M158" s="7" t="inlineStr"/>
       <c r="N158" s="7" t="inlineStr">
         <is>
+          <t>+234 811 279 1242</t>
+        </is>
+      </c>
+      <c r="O158" s="7" t="inlineStr">
+        <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="O158" s="7" t="inlineStr">
+      <c r="P158" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P158" s="7" t="inlineStr">
+      <c r="Q158" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q158" s="7" t="inlineStr">
+      <c r="R158" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R158" s="7" t="inlineStr"/>
-      <c r="S158" s="8" t="inlineStr"/>
+      <c r="S158" s="7" t="inlineStr"/>
       <c r="T158" s="8" t="inlineStr"/>
       <c r="U158" s="8" t="inlineStr"/>
       <c r="V158" s="8" t="inlineStr"/>
+      <c r="W158" s="8" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
@@ -15321,31 +15740,32 @@
           <t>+234 803 537 1101</t>
         </is>
       </c>
-      <c r="N159" s="7" t="inlineStr">
+      <c r="N159" s="7" t="inlineStr"/>
+      <c r="O159" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O159" s="7" t="inlineStr">
+      <c r="P159" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P159" s="7" t="inlineStr">
+      <c r="Q159" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q159" s="7" t="inlineStr">
+      <c r="R159" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R159" s="7" t="inlineStr"/>
-      <c r="S159" s="8" t="inlineStr"/>
+      <c r="S159" s="7" t="inlineStr"/>
       <c r="T159" s="8" t="inlineStr"/>
       <c r="U159" s="8" t="inlineStr"/>
       <c r="V159" s="8" t="inlineStr"/>
+      <c r="W159" s="8" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
@@ -15413,31 +15833,32 @@
           <t>8060579056</t>
         </is>
       </c>
-      <c r="N160" s="7" t="inlineStr">
+      <c r="N160" s="7" t="inlineStr"/>
+      <c r="O160" s="7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O160" s="7" t="inlineStr">
+      <c r="P160" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P160" s="7" t="inlineStr">
+      <c r="Q160" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q160" s="7" t="inlineStr">
+      <c r="R160" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R160" s="7" t="inlineStr"/>
-      <c r="S160" s="8" t="inlineStr"/>
+      <c r="S160" s="7" t="inlineStr"/>
       <c r="T160" s="8" t="inlineStr"/>
       <c r="U160" s="8" t="inlineStr"/>
       <c r="V160" s="8" t="inlineStr"/>
+      <c r="W160" s="8" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -15503,29 +15924,34 @@
       <c r="M161" s="7" t="inlineStr"/>
       <c r="N161" s="7" t="inlineStr">
         <is>
+          <t>+234 809 999 9654</t>
+        </is>
+      </c>
+      <c r="O161" s="7" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O161" s="7" t="inlineStr">
+      <c r="P161" s="7" t="inlineStr">
         <is>
           <t>facilities services</t>
         </is>
       </c>
-      <c r="P161" s="7" t="inlineStr">
+      <c r="Q161" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q161" s="7" t="inlineStr">
+      <c r="R161" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R161" s="7" t="inlineStr"/>
-      <c r="S161" s="8" t="inlineStr"/>
+      <c r="S161" s="7" t="inlineStr"/>
       <c r="T161" s="8" t="inlineStr"/>
       <c r="U161" s="8" t="inlineStr"/>
       <c r="V161" s="8" t="inlineStr"/>
+      <c r="W161" s="8" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -15591,29 +16017,34 @@
       <c r="M162" s="7" t="inlineStr"/>
       <c r="N162" s="7" t="inlineStr">
         <is>
+          <t>+20 10 01147139</t>
+        </is>
+      </c>
+      <c r="O162" s="7" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O162" s="7" t="inlineStr">
+      <c r="P162" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P162" s="7" t="inlineStr">
+      <c r="Q162" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q162" s="7" t="inlineStr">
+      <c r="R162" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R162" s="7" t="inlineStr"/>
-      <c r="S162" s="8" t="inlineStr"/>
+      <c r="S162" s="7" t="inlineStr"/>
       <c r="T162" s="8" t="inlineStr"/>
       <c r="U162" s="8" t="inlineStr"/>
       <c r="V162" s="8" t="inlineStr"/>
+      <c r="W162" s="8" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
@@ -15683,29 +16114,34 @@
       </c>
       <c r="N163" s="7" t="inlineStr">
         <is>
+          <t>+91 97250 53464</t>
+        </is>
+      </c>
+      <c r="O163" s="7" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="O163" s="7" t="inlineStr">
+      <c r="P163" s="7" t="inlineStr">
         <is>
           <t>mechanical or industrial engineering</t>
         </is>
       </c>
-      <c r="P163" s="7" t="inlineStr">
+      <c r="Q163" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q163" s="7" t="inlineStr">
+      <c r="R163" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R163" s="7" t="inlineStr"/>
-      <c r="S163" s="8" t="inlineStr"/>
+      <c r="S163" s="7" t="inlineStr"/>
       <c r="T163" s="8" t="inlineStr"/>
       <c r="U163" s="8" t="inlineStr"/>
       <c r="V163" s="8" t="inlineStr"/>
+      <c r="W163" s="8" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
@@ -15775,29 +16211,34 @@
       </c>
       <c r="N164" s="7" t="inlineStr">
         <is>
+          <t>+234 803 706 2847</t>
+        </is>
+      </c>
+      <c r="O164" s="7" t="inlineStr">
+        <is>
           <t>470</t>
         </is>
       </c>
-      <c r="O164" s="7" t="inlineStr">
+      <c r="P164" s="7" t="inlineStr">
         <is>
           <t>logistics &amp; supply chain</t>
         </is>
       </c>
-      <c r="P164" s="7" t="inlineStr">
+      <c r="Q164" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q164" s="7" t="inlineStr">
+      <c r="R164" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R164" s="7" t="inlineStr"/>
-      <c r="S164" s="8" t="inlineStr"/>
+      <c r="S164" s="7" t="inlineStr"/>
       <c r="T164" s="8" t="inlineStr"/>
       <c r="U164" s="8" t="inlineStr"/>
       <c r="V164" s="8" t="inlineStr"/>
+      <c r="W164" s="8" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
@@ -15861,31 +16302,32 @@
           <t>+234 809 033 5116</t>
         </is>
       </c>
-      <c r="N165" s="7" t="inlineStr">
+      <c r="N165" s="7" t="inlineStr"/>
+      <c r="O165" s="7" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="O165" s="7" t="inlineStr">
+      <c r="P165" s="7" t="inlineStr">
         <is>
           <t>maritime</t>
         </is>
       </c>
-      <c r="P165" s="7" t="inlineStr">
+      <c r="Q165" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q165" s="7" t="inlineStr">
+      <c r="R165" s="7" t="inlineStr">
         <is>
           <t>Ms.</t>
         </is>
       </c>
-      <c r="R165" s="7" t="inlineStr"/>
-      <c r="S165" s="8" t="inlineStr"/>
+      <c r="S165" s="7" t="inlineStr"/>
       <c r="T165" s="8" t="inlineStr"/>
       <c r="U165" s="8" t="inlineStr"/>
       <c r="V165" s="8" t="inlineStr"/>
+      <c r="W165" s="8" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
@@ -15953,31 +16395,32 @@
           <t>+234 1 440 8433</t>
         </is>
       </c>
-      <c r="N166" s="7" t="inlineStr">
+      <c r="N166" s="7" t="inlineStr"/>
+      <c r="O166" s="7" t="inlineStr">
         <is>
           <t>2500</t>
         </is>
       </c>
-      <c r="O166" s="7" t="inlineStr">
+      <c r="P166" s="7" t="inlineStr">
         <is>
           <t>maritime</t>
         </is>
       </c>
-      <c r="P166" s="7" t="inlineStr">
+      <c r="Q166" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q166" s="7" t="inlineStr">
+      <c r="R166" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R166" s="7" t="inlineStr"/>
-      <c r="S166" s="8" t="inlineStr"/>
+      <c r="S166" s="7" t="inlineStr"/>
       <c r="T166" s="8" t="inlineStr"/>
       <c r="U166" s="8" t="inlineStr"/>
       <c r="V166" s="8" t="inlineStr"/>
+      <c r="W166" s="8" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
@@ -16047,29 +16490,34 @@
       </c>
       <c r="N167" s="7" t="inlineStr">
         <is>
+          <t>+234 805 729 1412</t>
+        </is>
+      </c>
+      <c r="O167" s="7" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="O167" s="7" t="inlineStr">
+      <c r="P167" s="7" t="inlineStr">
         <is>
           <t>maritime</t>
         </is>
       </c>
-      <c r="P167" s="7" t="inlineStr">
+      <c r="Q167" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q167" s="7" t="inlineStr">
+      <c r="R167" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R167" s="7" t="inlineStr"/>
-      <c r="S167" s="8" t="inlineStr"/>
+      <c r="S167" s="7" t="inlineStr"/>
       <c r="T167" s="8" t="inlineStr"/>
       <c r="U167" s="8" t="inlineStr"/>
       <c r="V167" s="8" t="inlineStr"/>
+      <c r="W167" s="8" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -16139,29 +16587,34 @@
       </c>
       <c r="N168" s="7" t="inlineStr">
         <is>
+          <t>+234 701 700 2128</t>
+        </is>
+      </c>
+      <c r="O168" s="7" t="inlineStr">
+        <is>
           <t>3800</t>
         </is>
       </c>
-      <c r="O168" s="7" t="inlineStr">
+      <c r="P168" s="7" t="inlineStr">
         <is>
           <t>logistics &amp; supply chain</t>
         </is>
       </c>
-      <c r="P168" s="7" t="inlineStr">
+      <c r="Q168" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q168" s="7" t="inlineStr">
+      <c r="R168" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R168" s="7" t="inlineStr"/>
-      <c r="S168" s="8" t="inlineStr"/>
+      <c r="S168" s="7" t="inlineStr"/>
       <c r="T168" s="8" t="inlineStr"/>
       <c r="U168" s="8" t="inlineStr"/>
       <c r="V168" s="8" t="inlineStr"/>
+      <c r="W168" s="8" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -16229,31 +16682,32 @@
           <t>+234 707 499 1046</t>
         </is>
       </c>
-      <c r="N169" s="7" t="inlineStr">
+      <c r="N169" s="7" t="inlineStr"/>
+      <c r="O169" s="7" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="O169" s="7" t="inlineStr">
+      <c r="P169" s="7" t="inlineStr">
         <is>
           <t>maritime</t>
         </is>
       </c>
-      <c r="P169" s="7" t="inlineStr">
+      <c r="Q169" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q169" s="7" t="inlineStr">
+      <c r="R169" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R169" s="7" t="inlineStr"/>
-      <c r="S169" s="8" t="inlineStr"/>
+      <c r="S169" s="7" t="inlineStr"/>
       <c r="T169" s="8" t="inlineStr"/>
       <c r="U169" s="8" t="inlineStr"/>
       <c r="V169" s="8" t="inlineStr"/>
+      <c r="W169" s="8" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
@@ -16321,31 +16775,32 @@
           <t>+234 1 277 8400</t>
         </is>
       </c>
-      <c r="N170" s="7" t="inlineStr">
+      <c r="N170" s="7" t="inlineStr"/>
+      <c r="O170" s="7" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="O170" s="7" t="inlineStr">
+      <c r="P170" s="7" t="inlineStr">
         <is>
           <t>maritime</t>
         </is>
       </c>
-      <c r="P170" s="7" t="inlineStr">
+      <c r="Q170" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q170" s="7" t="inlineStr">
+      <c r="R170" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R170" s="7" t="inlineStr"/>
-      <c r="S170" s="8" t="inlineStr"/>
+      <c r="S170" s="7" t="inlineStr"/>
       <c r="T170" s="8" t="inlineStr"/>
       <c r="U170" s="8" t="inlineStr"/>
       <c r="V170" s="8" t="inlineStr"/>
+      <c r="W170" s="8" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
@@ -16413,31 +16868,32 @@
           <t>+234 701 683 6812</t>
         </is>
       </c>
-      <c r="N171" s="7" t="inlineStr">
+      <c r="N171" s="7" t="inlineStr"/>
+      <c r="O171" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O171" s="7" t="inlineStr">
+      <c r="P171" s="7" t="inlineStr">
         <is>
           <t>import &amp; export</t>
         </is>
       </c>
-      <c r="P171" s="7" t="inlineStr">
+      <c r="Q171" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q171" s="7" t="inlineStr">
+      <c r="R171" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R171" s="7" t="inlineStr"/>
-      <c r="S171" s="8" t="inlineStr"/>
+      <c r="S171" s="7" t="inlineStr"/>
       <c r="T171" s="8" t="inlineStr"/>
       <c r="U171" s="8" t="inlineStr"/>
       <c r="V171" s="8" t="inlineStr"/>
+      <c r="W171" s="8" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
@@ -16505,31 +16961,32 @@
           <t>+234 1 279 0684</t>
         </is>
       </c>
-      <c r="N172" s="7" t="inlineStr">
+      <c r="N172" s="7" t="inlineStr"/>
+      <c r="O172" s="7" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="O172" s="7" t="inlineStr">
+      <c r="P172" s="7" t="inlineStr">
         <is>
           <t>logistics &amp; supply chain</t>
         </is>
       </c>
-      <c r="P172" s="7" t="inlineStr">
+      <c r="Q172" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q172" s="7" t="inlineStr">
+      <c r="R172" s="7" t="inlineStr">
         <is>
           <t>Ms.</t>
         </is>
       </c>
-      <c r="R172" s="7" t="inlineStr"/>
-      <c r="S172" s="8" t="inlineStr"/>
+      <c r="S172" s="7" t="inlineStr"/>
       <c r="T172" s="8" t="inlineStr"/>
       <c r="U172" s="8" t="inlineStr"/>
       <c r="V172" s="8" t="inlineStr"/>
+      <c r="W172" s="8" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
@@ -16595,29 +17052,34 @@
       <c r="M173" s="7" t="inlineStr"/>
       <c r="N173" s="7" t="inlineStr">
         <is>
+          <t>+234 703 372 3763</t>
+        </is>
+      </c>
+      <c r="O173" s="7" t="inlineStr">
+        <is>
           <t>650</t>
         </is>
       </c>
-      <c r="O173" s="7" t="inlineStr">
+      <c r="P173" s="7" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="P173" s="7" t="inlineStr">
+      <c r="Q173" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q173" s="7" t="inlineStr">
+      <c r="R173" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R173" s="7" t="inlineStr"/>
-      <c r="S173" s="8" t="inlineStr"/>
+      <c r="S173" s="7" t="inlineStr"/>
       <c r="T173" s="8" t="inlineStr"/>
       <c r="U173" s="8" t="inlineStr"/>
       <c r="V173" s="8" t="inlineStr"/>
+      <c r="W173" s="8" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
@@ -16681,31 +17143,32 @@
         </is>
       </c>
       <c r="M174" s="7" t="inlineStr"/>
-      <c r="N174" s="7" t="inlineStr">
+      <c r="N174" s="7" t="inlineStr"/>
+      <c r="O174" s="7" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="O174" s="7" t="inlineStr">
+      <c r="P174" s="7" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="P174" s="7" t="inlineStr">
+      <c r="Q174" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q174" s="7" t="inlineStr">
+      <c r="R174" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R174" s="7" t="inlineStr"/>
-      <c r="S174" s="8" t="inlineStr"/>
+      <c r="S174" s="7" t="inlineStr"/>
       <c r="T174" s="8" t="inlineStr"/>
       <c r="U174" s="8" t="inlineStr"/>
       <c r="V174" s="8" t="inlineStr"/>
+      <c r="W174" s="8" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -16769,31 +17232,32 @@
         </is>
       </c>
       <c r="M175" s="7" t="inlineStr"/>
-      <c r="N175" s="7" t="inlineStr">
+      <c r="N175" s="7" t="inlineStr"/>
+      <c r="O175" s="7" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="O175" s="7" t="inlineStr">
+      <c r="P175" s="7" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="P175" s="7" t="inlineStr">
+      <c r="Q175" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q175" s="7" t="inlineStr">
+      <c r="R175" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R175" s="7" t="inlineStr"/>
-      <c r="S175" s="8" t="inlineStr"/>
+      <c r="S175" s="7" t="inlineStr"/>
       <c r="T175" s="8" t="inlineStr"/>
       <c r="U175" s="8" t="inlineStr"/>
       <c r="V175" s="8" t="inlineStr"/>
+      <c r="W175" s="8" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -16857,31 +17321,32 @@
         </is>
       </c>
       <c r="M176" s="7" t="inlineStr"/>
-      <c r="N176" s="7" t="inlineStr">
+      <c r="N176" s="7" t="inlineStr"/>
+      <c r="O176" s="7" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="O176" s="7" t="inlineStr">
+      <c r="P176" s="7" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="P176" s="7" t="inlineStr">
+      <c r="Q176" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q176" s="7" t="inlineStr">
+      <c r="R176" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R176" s="7" t="inlineStr"/>
-      <c r="S176" s="8" t="inlineStr"/>
+      <c r="S176" s="7" t="inlineStr"/>
       <c r="T176" s="8" t="inlineStr"/>
       <c r="U176" s="8" t="inlineStr"/>
       <c r="V176" s="8" t="inlineStr"/>
+      <c r="W176" s="8" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
@@ -16945,31 +17410,32 @@
         </is>
       </c>
       <c r="M177" s="7" t="inlineStr"/>
-      <c r="N177" s="7" t="inlineStr">
+      <c r="N177" s="7" t="inlineStr"/>
+      <c r="O177" s="7" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="O177" s="7" t="inlineStr">
+      <c r="P177" s="7" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="P177" s="7" t="inlineStr">
+      <c r="Q177" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q177" s="7" t="inlineStr">
+      <c r="R177" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R177" s="7" t="inlineStr"/>
-      <c r="S177" s="8" t="inlineStr"/>
+      <c r="S177" s="7" t="inlineStr"/>
       <c r="T177" s="8" t="inlineStr"/>
       <c r="U177" s="8" t="inlineStr"/>
       <c r="V177" s="8" t="inlineStr"/>
+      <c r="W177" s="8" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
@@ -17037,31 +17503,32 @@
           <t>+234 54 342 640</t>
         </is>
       </c>
-      <c r="N178" s="7" t="inlineStr">
+      <c r="N178" s="7" t="inlineStr"/>
+      <c r="O178" s="7" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="O178" s="7" t="inlineStr">
+      <c r="P178" s="7" t="inlineStr">
         <is>
           <t>electrical/electronic manufacturing</t>
         </is>
       </c>
-      <c r="P178" s="7" t="inlineStr">
+      <c r="Q178" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q178" s="7" t="inlineStr">
+      <c r="R178" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R178" s="7" t="inlineStr"/>
-      <c r="S178" s="8" t="inlineStr"/>
+      <c r="S178" s="7" t="inlineStr"/>
       <c r="T178" s="8" t="inlineStr"/>
       <c r="U178" s="8" t="inlineStr"/>
       <c r="V178" s="8" t="inlineStr"/>
+      <c r="W178" s="8" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
@@ -17129,31 +17596,32 @@
           <t>+234 700 123 9999</t>
         </is>
       </c>
-      <c r="N179" s="7" t="inlineStr">
+      <c r="N179" s="7" t="inlineStr"/>
+      <c r="O179" s="7" t="inlineStr">
         <is>
           <t>2500</t>
         </is>
       </c>
-      <c r="O179" s="7" t="inlineStr">
+      <c r="P179" s="7" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="P179" s="7" t="inlineStr">
+      <c r="Q179" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q179" s="7" t="inlineStr">
+      <c r="R179" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R179" s="7" t="inlineStr"/>
-      <c r="S179" s="8" t="inlineStr"/>
+      <c r="S179" s="7" t="inlineStr"/>
       <c r="T179" s="8" t="inlineStr"/>
       <c r="U179" s="8" t="inlineStr"/>
       <c r="V179" s="8" t="inlineStr"/>
+      <c r="W179" s="8" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
@@ -17221,31 +17689,32 @@
           <t>+234 906 246 0009</t>
         </is>
       </c>
-      <c r="N180" s="7" t="inlineStr">
+      <c r="N180" s="7" t="inlineStr"/>
+      <c r="O180" s="7" t="inlineStr">
         <is>
           <t>750</t>
         </is>
       </c>
-      <c r="O180" s="7" t="inlineStr">
+      <c r="P180" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P180" s="7" t="inlineStr">
+      <c r="Q180" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q180" s="7" t="inlineStr">
+      <c r="R180" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R180" s="7" t="inlineStr"/>
-      <c r="S180" s="8" t="inlineStr"/>
+      <c r="S180" s="7" t="inlineStr"/>
       <c r="T180" s="8" t="inlineStr"/>
       <c r="U180" s="8" t="inlineStr"/>
       <c r="V180" s="8" t="inlineStr"/>
+      <c r="W180" s="8" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
@@ -17313,31 +17782,32 @@
           <t>+971 4 260 2628</t>
         </is>
       </c>
-      <c r="N181" s="7" t="inlineStr">
+      <c r="N181" s="7" t="inlineStr"/>
+      <c r="O181" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O181" s="7" t="inlineStr">
+      <c r="P181" s="7" t="inlineStr">
         <is>
           <t>investment management</t>
         </is>
       </c>
-      <c r="P181" s="7" t="inlineStr">
+      <c r="Q181" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q181" s="7" t="inlineStr">
+      <c r="R181" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R181" s="7" t="inlineStr"/>
-      <c r="S181" s="8" t="inlineStr"/>
+      <c r="S181" s="7" t="inlineStr"/>
       <c r="T181" s="8" t="inlineStr"/>
       <c r="U181" s="8" t="inlineStr"/>
       <c r="V181" s="8" t="inlineStr"/>
+      <c r="W181" s="8" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -17403,29 +17873,34 @@
       <c r="M182" s="7" t="inlineStr"/>
       <c r="N182" s="7" t="inlineStr">
         <is>
+          <t>+234 812 945 1889</t>
+        </is>
+      </c>
+      <c r="O182" s="7" t="inlineStr">
+        <is>
           <t>750</t>
         </is>
       </c>
-      <c r="O182" s="7" t="inlineStr">
+      <c r="P182" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P182" s="7" t="inlineStr">
+      <c r="Q182" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q182" s="7" t="inlineStr">
+      <c r="R182" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R182" s="7" t="inlineStr"/>
-      <c r="S182" s="8" t="inlineStr"/>
+      <c r="S182" s="7" t="inlineStr"/>
       <c r="T182" s="8" t="inlineStr"/>
       <c r="U182" s="8" t="inlineStr"/>
       <c r="V182" s="8" t="inlineStr"/>
+      <c r="W182" s="8" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -17495,29 +17970,34 @@
       </c>
       <c r="N183" s="7" t="inlineStr">
         <is>
+          <t>+234 703 404 7830</t>
+        </is>
+      </c>
+      <c r="O183" s="7" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="O183" s="7" t="inlineStr">
+      <c r="P183" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P183" s="7" t="inlineStr">
+      <c r="Q183" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q183" s="7" t="inlineStr">
+      <c r="R183" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R183" s="7" t="inlineStr"/>
-      <c r="S183" s="8" t="inlineStr"/>
+      <c r="S183" s="7" t="inlineStr"/>
       <c r="T183" s="8" t="inlineStr"/>
       <c r="U183" s="8" t="inlineStr"/>
       <c r="V183" s="8" t="inlineStr"/>
+      <c r="W183" s="8" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
@@ -17585,31 +18065,32 @@
           <t>+234 201 888 5300</t>
         </is>
       </c>
-      <c r="N184" s="7" t="inlineStr">
+      <c r="N184" s="7" t="inlineStr"/>
+      <c r="O184" s="7" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="O184" s="7" t="inlineStr">
+      <c r="P184" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P184" s="7" t="inlineStr">
+      <c r="Q184" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q184" s="7" t="inlineStr">
+      <c r="R184" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R184" s="7" t="inlineStr"/>
-      <c r="S184" s="8" t="inlineStr"/>
+      <c r="S184" s="7" t="inlineStr"/>
       <c r="T184" s="8" t="inlineStr"/>
       <c r="U184" s="8" t="inlineStr"/>
       <c r="V184" s="8" t="inlineStr"/>
+      <c r="W184" s="8" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
@@ -17677,31 +18158,32 @@
           <t>+234 809 466 6668</t>
         </is>
       </c>
-      <c r="N185" s="7" t="inlineStr">
+      <c r="N185" s="7" t="inlineStr"/>
+      <c r="O185" s="7" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O185" s="7" t="inlineStr">
+      <c r="P185" s="7" t="inlineStr">
         <is>
           <t>logistics &amp; supply chain</t>
         </is>
       </c>
-      <c r="P185" s="7" t="inlineStr">
+      <c r="Q185" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q185" s="7" t="inlineStr">
+      <c r="R185" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R185" s="7" t="inlineStr"/>
-      <c r="S185" s="8" t="inlineStr"/>
+      <c r="S185" s="7" t="inlineStr"/>
       <c r="T185" s="8" t="inlineStr"/>
       <c r="U185" s="8" t="inlineStr"/>
       <c r="V185" s="8" t="inlineStr"/>
+      <c r="W185" s="8" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
@@ -17769,31 +18251,32 @@
           <t>+234 201 453 3754</t>
         </is>
       </c>
-      <c r="N186" s="7" t="inlineStr">
+      <c r="N186" s="7" t="inlineStr"/>
+      <c r="O186" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O186" s="7" t="inlineStr">
+      <c r="P186" s="7" t="inlineStr">
         <is>
           <t>international trade &amp; development</t>
         </is>
       </c>
-      <c r="P186" s="7" t="inlineStr">
+      <c r="Q186" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q186" s="7" t="inlineStr">
+      <c r="R186" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R186" s="7" t="inlineStr"/>
-      <c r="S186" s="8" t="inlineStr"/>
+      <c r="S186" s="7" t="inlineStr"/>
       <c r="T186" s="8" t="inlineStr"/>
       <c r="U186" s="8" t="inlineStr"/>
       <c r="V186" s="8" t="inlineStr"/>
+      <c r="W186" s="8" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
@@ -17861,31 +18344,32 @@
           <t>+91 22 6666 3666</t>
         </is>
       </c>
-      <c r="N187" s="7" t="inlineStr">
+      <c r="N187" s="7" t="inlineStr"/>
+      <c r="O187" s="7" t="inlineStr">
         <is>
           <t>370</t>
         </is>
       </c>
-      <c r="O187" s="7" t="inlineStr">
+      <c r="P187" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P187" s="7" t="inlineStr">
+      <c r="Q187" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q187" s="7" t="inlineStr">
+      <c r="R187" s="7" t="inlineStr">
         <is>
           <t>Ms.</t>
         </is>
       </c>
-      <c r="R187" s="7" t="inlineStr"/>
-      <c r="S187" s="8" t="inlineStr"/>
+      <c r="S187" s="7" t="inlineStr"/>
       <c r="T187" s="8" t="inlineStr"/>
       <c r="U187" s="8" t="inlineStr"/>
       <c r="V187" s="8" t="inlineStr"/>
+      <c r="W187" s="8" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
@@ -17955,33 +18439,38 @@
       </c>
       <c r="N188" s="7" t="inlineStr">
         <is>
+          <t>+234 803 613 5171</t>
+        </is>
+      </c>
+      <c r="O188" s="7" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="O188" s="7" t="inlineStr">
+      <c r="P188" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P188" s="7" t="inlineStr">
+      <c r="Q188" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q188" s="7" t="inlineStr">
+      <c r="R188" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R188" s="9" t="inlineStr">
+      <c r="S188" s="9" t="inlineStr">
         <is>
           <t>check gender before sending</t>
         </is>
       </c>
-      <c r="S188" s="8" t="inlineStr"/>
       <c r="T188" s="8" t="inlineStr"/>
       <c r="U188" s="8" t="inlineStr"/>
       <c r="V188" s="8" t="inlineStr"/>
+      <c r="W188" s="8" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
@@ -18049,31 +18538,32 @@
           <t>+1 469-726-4780</t>
         </is>
       </c>
-      <c r="N189" s="7" t="inlineStr">
+      <c r="N189" s="7" t="inlineStr"/>
+      <c r="O189" s="7" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="O189" s="7" t="inlineStr">
+      <c r="P189" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P189" s="7" t="inlineStr">
+      <c r="Q189" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q189" s="7" t="inlineStr">
+      <c r="R189" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R189" s="7" t="inlineStr"/>
-      <c r="S189" s="8" t="inlineStr"/>
+      <c r="S189" s="7" t="inlineStr"/>
       <c r="T189" s="8" t="inlineStr"/>
       <c r="U189" s="8" t="inlineStr"/>
       <c r="V189" s="8" t="inlineStr"/>
+      <c r="W189" s="8" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
@@ -18137,31 +18627,32 @@
         </is>
       </c>
       <c r="M190" s="7" t="inlineStr"/>
-      <c r="N190" s="7" t="inlineStr">
+      <c r="N190" s="7" t="inlineStr"/>
+      <c r="O190" s="7" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O190" s="7" t="inlineStr">
+      <c r="P190" s="7" t="inlineStr">
         <is>
           <t>renewables &amp; environment</t>
         </is>
       </c>
-      <c r="P190" s="7" t="inlineStr">
+      <c r="Q190" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q190" s="7" t="inlineStr">
+      <c r="R190" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R190" s="7" t="inlineStr"/>
-      <c r="S190" s="8" t="inlineStr"/>
+      <c r="S190" s="7" t="inlineStr"/>
       <c r="T190" s="8" t="inlineStr"/>
       <c r="U190" s="8" t="inlineStr"/>
       <c r="V190" s="8" t="inlineStr"/>
+      <c r="W190" s="8" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
@@ -18229,31 +18720,32 @@
           <t>+234 706 966 1694</t>
         </is>
       </c>
-      <c r="N191" s="7" t="inlineStr">
+      <c r="N191" s="7" t="inlineStr"/>
+      <c r="O191" s="7" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="O191" s="7" t="inlineStr">
+      <c r="P191" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P191" s="7" t="inlineStr">
+      <c r="Q191" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q191" s="7" t="inlineStr">
+      <c r="R191" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R191" s="7" t="inlineStr"/>
-      <c r="S191" s="8" t="inlineStr"/>
+      <c r="S191" s="7" t="inlineStr"/>
       <c r="T191" s="8" t="inlineStr"/>
       <c r="U191" s="8" t="inlineStr"/>
       <c r="V191" s="8" t="inlineStr"/>
+      <c r="W191" s="8" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
@@ -18323,29 +18815,34 @@
       </c>
       <c r="N192" s="7" t="inlineStr">
         <is>
+          <t>+234 703 410 6027</t>
+        </is>
+      </c>
+      <c r="O192" s="7" t="inlineStr">
+        <is>
           <t>650</t>
         </is>
       </c>
-      <c r="O192" s="7" t="inlineStr">
+      <c r="P192" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P192" s="7" t="inlineStr">
+      <c r="Q192" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q192" s="7" t="inlineStr">
+      <c r="R192" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R192" s="7" t="inlineStr"/>
-      <c r="S192" s="8" t="inlineStr"/>
+      <c r="S192" s="7" t="inlineStr"/>
       <c r="T192" s="8" t="inlineStr"/>
       <c r="U192" s="8" t="inlineStr"/>
       <c r="V192" s="8" t="inlineStr"/>
+      <c r="W192" s="8" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
@@ -18415,29 +18912,34 @@
       </c>
       <c r="N193" s="7" t="inlineStr">
         <is>
+          <t>+234 803 545 0671</t>
+        </is>
+      </c>
+      <c r="O193" s="7" t="inlineStr">
+        <is>
           <t>650</t>
         </is>
       </c>
-      <c r="O193" s="7" t="inlineStr">
+      <c r="P193" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P193" s="7" t="inlineStr">
+      <c r="Q193" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q193" s="7" t="inlineStr">
+      <c r="R193" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R193" s="7" t="inlineStr"/>
-      <c r="S193" s="8" t="inlineStr"/>
+      <c r="S193" s="7" t="inlineStr"/>
       <c r="T193" s="8" t="inlineStr"/>
       <c r="U193" s="8" t="inlineStr"/>
       <c r="V193" s="8" t="inlineStr"/>
+      <c r="W193" s="8" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
@@ -18497,31 +18999,32 @@
       </c>
       <c r="L194" s="7" t="inlineStr"/>
       <c r="M194" s="7" t="inlineStr"/>
-      <c r="N194" s="7" t="inlineStr">
+      <c r="N194" s="7" t="inlineStr"/>
+      <c r="O194" s="7" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="O194" s="7" t="inlineStr">
+      <c r="P194" s="7" t="inlineStr">
         <is>
           <t>mining &amp; metals</t>
         </is>
       </c>
-      <c r="P194" s="7" t="inlineStr">
+      <c r="Q194" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q194" s="7" t="inlineStr">
+      <c r="R194" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R194" s="7" t="inlineStr"/>
-      <c r="S194" s="8" t="inlineStr"/>
+      <c r="S194" s="7" t="inlineStr"/>
       <c r="T194" s="8" t="inlineStr"/>
       <c r="U194" s="8" t="inlineStr"/>
       <c r="V194" s="8" t="inlineStr"/>
+      <c r="W194" s="8" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
@@ -18589,31 +19092,32 @@
           <t>+234 806 789 5743</t>
         </is>
       </c>
-      <c r="N195" s="7" t="inlineStr">
+      <c r="N195" s="7" t="inlineStr"/>
+      <c r="O195" s="7" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="O195" s="7" t="inlineStr">
+      <c r="P195" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P195" s="7" t="inlineStr">
+      <c r="Q195" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q195" s="7" t="inlineStr">
+      <c r="R195" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R195" s="7" t="inlineStr"/>
-      <c r="S195" s="8" t="inlineStr"/>
+      <c r="S195" s="7" t="inlineStr"/>
       <c r="T195" s="8" t="inlineStr"/>
       <c r="U195" s="8" t="inlineStr"/>
       <c r="V195" s="8" t="inlineStr"/>
+      <c r="W195" s="8" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -18681,31 +19185,32 @@
           <t>+1 573-323-4404</t>
         </is>
       </c>
-      <c r="N196" s="7" t="inlineStr">
+      <c r="N196" s="7" t="inlineStr"/>
+      <c r="O196" s="7" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="O196" s="7" t="inlineStr">
+      <c r="P196" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P196" s="7" t="inlineStr">
+      <c r="Q196" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q196" s="7" t="inlineStr">
+      <c r="R196" s="7" t="inlineStr">
         <is>
           <t>Ms.</t>
         </is>
       </c>
-      <c r="R196" s="7" t="inlineStr"/>
-      <c r="S196" s="8" t="inlineStr"/>
+      <c r="S196" s="7" t="inlineStr"/>
       <c r="T196" s="8" t="inlineStr"/>
       <c r="U196" s="8" t="inlineStr"/>
       <c r="V196" s="8" t="inlineStr"/>
+      <c r="W196" s="8" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -18775,29 +19280,34 @@
       </c>
       <c r="N197" s="7" t="inlineStr">
         <is>
+          <t>+234 803 709 7718</t>
+        </is>
+      </c>
+      <c r="O197" s="7" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="O197" s="7" t="inlineStr">
+      <c r="P197" s="7" t="inlineStr">
         <is>
           <t>oil &amp; energy</t>
         </is>
       </c>
-      <c r="P197" s="7" t="inlineStr">
+      <c r="Q197" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q197" s="7" t="inlineStr">
+      <c r="R197" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R197" s="7" t="inlineStr"/>
-      <c r="S197" s="8" t="inlineStr"/>
+      <c r="S197" s="7" t="inlineStr"/>
       <c r="T197" s="8" t="inlineStr"/>
       <c r="U197" s="8" t="inlineStr"/>
       <c r="V197" s="8" t="inlineStr"/>
+      <c r="W197" s="8" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
@@ -18867,29 +19377,34 @@
       </c>
       <c r="N198" s="7" t="inlineStr">
         <is>
+          <t>+234 806 018 6974</t>
+        </is>
+      </c>
+      <c r="O198" s="7" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="O198" s="7" t="inlineStr">
+      <c r="P198" s="7" t="inlineStr">
         <is>
           <t>consumer goods</t>
         </is>
       </c>
-      <c r="P198" s="7" t="inlineStr">
+      <c r="Q198" s="7" t="inlineStr">
         <is>
           <t>Crane, terminal and plant drives - firm lead times</t>
         </is>
       </c>
-      <c r="Q198" s="7" t="inlineStr">
+      <c r="R198" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R198" s="7" t="inlineStr"/>
-      <c r="S198" s="8" t="inlineStr"/>
+      <c r="S198" s="7" t="inlineStr"/>
       <c r="T198" s="8" t="inlineStr"/>
       <c r="U198" s="8" t="inlineStr"/>
       <c r="V198" s="8" t="inlineStr"/>
+      <c r="W198" s="8" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
@@ -18959,29 +19474,34 @@
       </c>
       <c r="N199" s="7" t="inlineStr">
         <is>
+          <t>+234 812 291 3391</t>
+        </is>
+      </c>
+      <c r="O199" s="7" t="inlineStr">
+        <is>
           <t>101000</t>
         </is>
       </c>
-      <c r="O199" s="7" t="inlineStr">
+      <c r="P199" s="7" t="inlineStr">
         <is>
           <t>renewables &amp; environment</t>
         </is>
       </c>
-      <c r="P199" s="7" t="inlineStr">
+      <c r="Q199" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q199" s="7" t="inlineStr">
+      <c r="R199" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R199" s="7" t="inlineStr"/>
-      <c r="S199" s="8" t="inlineStr"/>
+      <c r="S199" s="7" t="inlineStr"/>
       <c r="T199" s="8" t="inlineStr"/>
       <c r="U199" s="8" t="inlineStr"/>
       <c r="V199" s="8" t="inlineStr"/>
+      <c r="W199" s="8" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
@@ -19051,29 +19571,34 @@
       </c>
       <c r="N200" s="7" t="inlineStr">
         <is>
+          <t>+234 701 327 2750</t>
+        </is>
+      </c>
+      <c r="O200" s="7" t="inlineStr">
+        <is>
           <t>101000</t>
         </is>
       </c>
-      <c r="O200" s="7" t="inlineStr">
+      <c r="P200" s="7" t="inlineStr">
         <is>
           <t>renewables &amp; environment</t>
         </is>
       </c>
-      <c r="P200" s="7" t="inlineStr">
+      <c r="Q200" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q200" s="7" t="inlineStr">
+      <c r="R200" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R200" s="7" t="inlineStr"/>
-      <c r="S200" s="8" t="inlineStr"/>
+      <c r="S200" s="7" t="inlineStr"/>
       <c r="T200" s="8" t="inlineStr"/>
       <c r="U200" s="8" t="inlineStr"/>
       <c r="V200" s="8" t="inlineStr"/>
+      <c r="W200" s="8" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
@@ -19141,39 +19666,40 @@
           <t>+234 707 469 3837</t>
         </is>
       </c>
-      <c r="N201" s="7" t="inlineStr">
+      <c r="N201" s="7" t="inlineStr"/>
+      <c r="O201" s="7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O201" s="7" t="inlineStr">
+      <c r="P201" s="7" t="inlineStr">
         <is>
           <t>machinery</t>
         </is>
       </c>
-      <c r="P201" s="7" t="inlineStr">
+      <c r="Q201" s="7" t="inlineStr">
         <is>
           <t>Carry IMAK as a manufacturer line - distributor margin</t>
         </is>
       </c>
-      <c r="Q201" s="7" t="inlineStr">
+      <c r="R201" s="7" t="inlineStr">
         <is>
           <t>Mr.</t>
         </is>
       </c>
-      <c r="R201" s="7" t="inlineStr"/>
-      <c r="S201" s="8" t="inlineStr"/>
+      <c r="S201" s="7" t="inlineStr"/>
       <c r="T201" s="8" t="inlineStr"/>
       <c r="U201" s="8" t="inlineStr"/>
       <c r="V201" s="8" t="inlineStr"/>
+      <c r="W201" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V201"/>
+  <autoFilter ref="A1:W201"/>
   <dataValidations count="2">
-    <dataValidation sqref="S2:S201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T2:T201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Emailed,Replied,Meeting,Quoted,Won,Not interested"</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="V2:V201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19187,7 +19713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -19213,87 +19739,94 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
+          <t>DIRECT/MOBILE PHONE column: 80 of the 200 contacts have an Apollo-revealed personal mobile or direct number. Nigeria is a phone-first market - a WhatsApp message or call after your email doubles your chances. Numbers not found stay blank; the company switchboard is in the Company phone column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
           <t>Nigeria works in ENGLISH. The Salutation column gives Mr./Ms. per person.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr"/>
-    </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>NAME CHECK column (orange): several Nigerian (mostly Yoruba) first names are unisex - Kehinde, Ayodele, Damilola, Opeyemi and similar. Before writing Mr./Ms., glance at the LinkedIn photo - the link is in column K.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-    </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>TIER A = Distributors + Cement/Mining (recurring volume, big-ticket spares).</t>
-        </is>
-      </c>
+      <c r="A8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>TIER A = Distributors + Cement/Mining (recurring volume, big-ticket spares).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t>TIER B = Plants (replacement/spares business).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
-    </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Track progress in the yellow columns (Status / Date sent / Replied / Notes). Summary counts update when Excel recalculates (on open).</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Contacts worth knowing about:</t>
-        </is>
-      </c>
+      <c r="A13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>- C. Woermann Nigeria (5 contacts incl. Managing Director Klaus Okunowski): a German technical-trade house in Lagos since 1968 - they know exactly what a gearbox line is worth. Best distributor door in the file.</t>
+          <t>Contacts worth knowing about:</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>- Rotation &amp; Precision Machines (2 contacts): SKF bearings distributor, their own product keywords include 'gear motors and drives'. Directly relevant.</t>
+          <t>- C. Woermann Nigeria (5 contacts incl. Managing Director Klaus Okunowski): a German technical-trade house in Lagos since 1968 - they know exactly what a gearbox line is worth. Best distributor door in the file.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>- Dangote (8 contacts across Cement and Industries) and BUA (5) are at/near the company cap - the biggest plants in Africa.</t>
+          <t>- Rotation &amp; Precision Machines (2 contacts): SKF bearings distributor, their own product keywords include 'gear motors and drives'. Directly relevant.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>- Payment risk is real in Nigeria: agree terms before quoting; confirmed LC or advance payment is standard for first orders. Never ship against open account to a first-time buyer.</t>
+          <t>- Dangote (8 contacts across Cement and Industries) and BUA (5) are at/near the company cap - the biggest plants in Africa.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>- Payment risk is real in Nigeria: agree terms before quoting; confirmed LC or advance payment is standard for first orders. Never ship against open account to a first-time buyer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>- Egbin Power (5 contacts) is West Africa's biggest thermal power station.</t>
         </is>
